--- a/EL MIRADOR/Junio/JUNIO - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Junio/JUNIO - EL MIRADOR .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68643AE8-ECD8-44E1-AE12-22E70FD6A559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B644071F-8714-42A7-B182-6DC59008D528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1500,7 +1500,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1691,6 +1691,14 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1721,14 +1729,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1760,30 +1783,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2227,12 +2226,12 @@
     <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="131"/>
       <c r="B1" s="144"/>
-      <c r="C1" s="186" t="s">
+      <c r="C1" s="156" t="s">
         <v>302</v>
       </c>
-      <c r="D1" s="184"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
       <c r="G1" s="129"/>
       <c r="H1" s="129"/>
       <c r="I1" s="129"/>
@@ -2329,66 +2328,66 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="158" t="s">
         <v>296</v>
       </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="158"/>
+      <c r="F14" s="158"/>
+      <c r="G14" s="158"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="158"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="150"/>
-      <c r="B15" s="150"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="150"/>
+      <c r="A15" s="158"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="150"/>
-      <c r="B16" s="150"/>
-      <c r="C16" s="150"/>
-      <c r="D16" s="150"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
+      <c r="A16" s="158"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="158"/>
     </row>
     <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="150"/>
-      <c r="B17" s="150"/>
-      <c r="C17" s="150"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="150"/>
+      <c r="A17" s="158"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="158"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="158"/>
+      <c r="J17" s="158"/>
     </row>
     <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="150"/>
-      <c r="B18" s="150"/>
-      <c r="C18" s="150"/>
-      <c r="D18" s="150"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
+      <c r="A18" s="158"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="158"/>
+      <c r="J18" s="158"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
@@ -2975,7 +2974,7 @@
       </c>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
-      <c r="D51" s="177">
+      <c r="D51" s="150">
         <f>SUM(D48:D50)</f>
         <v>1382140.6</v>
       </c>
@@ -3106,7 +3105,7 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
-      <c r="D56" s="178"/>
+      <c r="D56" s="151"/>
       <c r="E56" s="47"/>
       <c r="F56" s="47"/>
       <c r="G56" s="47"/>
@@ -3304,7 +3303,7 @@
       <c r="C62" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D62" s="179">
+      <c r="D62" s="152">
         <v>27920.59</v>
       </c>
       <c r="E62" s="74">
@@ -3356,7 +3355,7 @@
       <c r="C63" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D63" s="179">
+      <c r="D63" s="152">
         <v>164905.93</v>
       </c>
       <c r="E63" s="74">
@@ -3509,7 +3508,7 @@
       </c>
       <c r="B67" s="36"/>
       <c r="C67" s="36"/>
-      <c r="D67" s="180"/>
+      <c r="D67" s="153"/>
       <c r="E67" s="74">
         <f>D67</f>
         <v>0</v>
@@ -4309,7 +4308,7 @@
         <v>7142595.8599999994</v>
       </c>
       <c r="E96" s="101">
-        <f t="shared" ref="D96:E96" si="15">SUM(E94+E51+E46+E92+E89+E82+E71+E60+E42+E37+E55)</f>
+        <f t="shared" ref="E96" si="15">SUM(E94+E51+E46+E92+E89+E82+E71+E60+E42+E37+E55)</f>
         <v>6729566.4766400009</v>
       </c>
       <c r="F96" s="101">
@@ -4369,7 +4368,7 @@
       <c r="A99" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C99" s="183">
+      <c r="C99" s="155">
         <f>90000-9000</f>
         <v>81000</v>
       </c>
@@ -4418,12 +4417,12 @@
       <c r="I103" s="65"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="156" t="s">
+      <c r="A104" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="B104" s="157"/>
-      <c r="C104" s="157"/>
-      <c r="D104" s="157"/>
+      <c r="B104" s="165"/>
+      <c r="C104" s="165"/>
+      <c r="D104" s="165"/>
       <c r="E104" s="91" t="s">
         <v>12</v>
       </c>
@@ -4444,8 +4443,8 @@
       </c>
     </row>
     <row r="105" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="158"/>
-      <c r="B105" s="159"/>
+      <c r="A105" s="166"/>
+      <c r="B105" s="167"/>
       <c r="C105" s="93"/>
       <c r="D105" s="45"/>
       <c r="E105" s="74">
@@ -4459,8 +4458,8 @@
       <c r="J105" s="63"/>
     </row>
     <row r="106" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="158"/>
-      <c r="B106" s="159"/>
+      <c r="A106" s="166"/>
+      <c r="B106" s="167"/>
       <c r="C106" s="93"/>
       <c r="D106" s="45"/>
       <c r="E106" s="74"/>
@@ -4471,11 +4470,11 @@
       <c r="J106" s="63"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="153" t="s">
+      <c r="A107" s="161" t="s">
         <v>18</v>
       </c>
-      <c r="B107" s="154"/>
-      <c r="C107" s="155"/>
+      <c r="B107" s="162"/>
+      <c r="C107" s="163"/>
       <c r="D107" s="90">
         <f>SUM(D105:D106)</f>
         <v>0</v>
@@ -4527,8 +4526,8 @@
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D112" s="152"/>
-      <c r="E112" s="152"/>
+      <c r="D112" s="160"/>
+      <c r="E112" s="160"/>
       <c r="F112" s="104"/>
       <c r="G112" s="104"/>
       <c r="H112" s="104"/>
@@ -4540,8 +4539,8 @@
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="19"/>
-      <c r="D113" s="152"/>
-      <c r="E113" s="152"/>
+      <c r="D113" s="160"/>
+      <c r="E113" s="160"/>
       <c r="F113" s="104"/>
       <c r="G113" s="104"/>
       <c r="H113" s="104"/>
@@ -4552,11 +4551,11 @@
         <v>24</v>
       </c>
       <c r="B114" s="9">
-        <v>0</v>
+        <v>7250000</v>
       </c>
       <c r="C114" s="21"/>
-      <c r="D114" s="152"/>
-      <c r="E114" s="152"/>
+      <c r="D114" s="160"/>
+      <c r="E114" s="160"/>
       <c r="F114" s="104"/>
       <c r="G114" s="104"/>
       <c r="H114" s="104"/>
@@ -4573,8 +4572,8 @@
       <c r="C115" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D115" s="152"/>
-      <c r="E115" s="152"/>
+      <c r="D115" s="160"/>
+      <c r="E115" s="160"/>
       <c r="F115" s="104"/>
       <c r="G115" s="104"/>
       <c r="H115" s="104"/>
@@ -4589,8 +4588,8 @@
         <v>-5642595.8599999994</v>
       </c>
       <c r="C116" s="19"/>
-      <c r="D116" s="152"/>
-      <c r="E116" s="152"/>
+      <c r="D116" s="160"/>
+      <c r="E116" s="160"/>
       <c r="F116" s="104"/>
       <c r="G116" s="104"/>
       <c r="H116" s="104"/>
@@ -4606,8 +4605,8 @@
         <v>0</v>
       </c>
       <c r="C117" s="19"/>
-      <c r="D117" s="152"/>
-      <c r="E117" s="152"/>
+      <c r="D117" s="160"/>
+      <c r="E117" s="160"/>
       <c r="F117" s="104"/>
       <c r="G117" s="104"/>
       <c r="H117" s="104"/>
@@ -4645,7 +4644,7 @@
       </c>
       <c r="B121" s="24">
         <f>SUM(B114:B120)</f>
-        <v>-5723595.8599999994</v>
+        <v>1526404.1400000006</v>
       </c>
       <c r="C121" s="79"/>
     </row>
@@ -4724,50 +4723,50 @@
       <c r="R131" s="10"/>
     </row>
     <row r="134" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B134" s="151"/>
-      <c r="C134" s="151"/>
-      <c r="D134" s="151"/>
-      <c r="E134" s="151"/>
+      <c r="B134" s="159"/>
+      <c r="C134" s="159"/>
+      <c r="D134" s="159"/>
+      <c r="E134" s="159"/>
       <c r="F134" s="108"/>
       <c r="G134" s="108"/>
       <c r="H134" s="108"/>
       <c r="I134" s="108"/>
     </row>
     <row r="135" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B135" s="151"/>
-      <c r="C135" s="151"/>
-      <c r="D135" s="151"/>
-      <c r="E135" s="151"/>
+      <c r="B135" s="159"/>
+      <c r="C135" s="159"/>
+      <c r="D135" s="159"/>
+      <c r="E135" s="159"/>
       <c r="F135" s="108"/>
       <c r="G135" s="108"/>
       <c r="H135" s="108"/>
       <c r="I135" s="108"/>
     </row>
     <row r="136" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B136" s="151"/>
-      <c r="C136" s="151"/>
-      <c r="D136" s="151"/>
-      <c r="E136" s="151"/>
+      <c r="B136" s="159"/>
+      <c r="C136" s="159"/>
+      <c r="D136" s="159"/>
+      <c r="E136" s="159"/>
       <c r="F136" s="108"/>
       <c r="G136" s="108"/>
       <c r="H136" s="108"/>
       <c r="I136" s="108"/>
     </row>
     <row r="137" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B137" s="151"/>
-      <c r="C137" s="151"/>
-      <c r="D137" s="151"/>
-      <c r="E137" s="151"/>
+      <c r="B137" s="159"/>
+      <c r="C137" s="159"/>
+      <c r="D137" s="159"/>
+      <c r="E137" s="159"/>
       <c r="F137" s="108"/>
       <c r="G137" s="108"/>
       <c r="H137" s="108"/>
       <c r="I137" s="108"/>
     </row>
     <row r="138" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B138" s="151"/>
-      <c r="C138" s="151"/>
-      <c r="D138" s="151"/>
-      <c r="E138" s="151"/>
+      <c r="B138" s="159"/>
+      <c r="C138" s="159"/>
+      <c r="D138" s="159"/>
+      <c r="E138" s="159"/>
       <c r="F138" s="108"/>
       <c r="G138" s="108"/>
       <c r="H138" s="108"/>
@@ -4825,11 +4824,11 @@
       <c r="J1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="177">
         <f>RESUMEN!D96-RESUMEN!D94</f>
         <v>5642595.8599999994</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="178"/>
       <c r="M1" s="77"/>
       <c r="N1" s="64"/>
     </row>
@@ -4895,60 +4894,60 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="173" t="s">
+      <c r="B5" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="161" t="s">
+      <c r="C5" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="175" t="s">
+      <c r="D5" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="161" t="s">
+      <c r="E5" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="161" t="s">
+      <c r="F5" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="161" t="s">
+      <c r="G5" s="168" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="168" t="s">
+      <c r="H5" s="181" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="166" t="s">
+      <c r="I5" s="179" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="166" t="s">
+      <c r="J5" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="171" t="s">
+      <c r="K5" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="166" t="s">
+      <c r="L5" s="179" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="166" t="s">
+      <c r="M5" s="179" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="162"/>
-      <c r="B6" s="174"/>
-      <c r="C6" s="162"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="162"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="167"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="170"/>
-      <c r="M6" s="167"/>
+      <c r="A6" s="169"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="180"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="185"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="180"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -4988,10 +4987,10 @@
         <v>75258.711480960017</v>
       </c>
       <c r="N7" s="138"/>
-      <c r="P7" s="160" t="s">
+      <c r="P7" s="174" t="s">
         <v>290</v>
       </c>
-      <c r="Q7" s="160"/>
+      <c r="Q7" s="174"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
@@ -5030,8 +5029,8 @@
         <v>89195.509903359998</v>
       </c>
       <c r="N8" s="138"/>
-      <c r="P8" s="160"/>
-      <c r="Q8" s="160"/>
+      <c r="P8" s="174"/>
+      <c r="Q8" s="174"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
@@ -5250,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="27">
-        <f t="shared" ref="J12:J43" si="5">L$2*E13</f>
+        <f t="shared" ref="J13:J43" si="5">L$2*E13</f>
         <v>59997.805223999989</v>
       </c>
       <c r="K13" s="86">
@@ -5799,7 +5798,7 @@
         <v>51426.690191999995</v>
       </c>
       <c r="K25" s="86">
-        <f t="shared" ref="K24:K55" si="10">I$3*E25%+I$4</f>
+        <f t="shared" ref="K25:K55" si="10">I$3*E25%+I$4</f>
         <v>0</v>
       </c>
       <c r="L25" s="9">
@@ -9635,7 +9634,7 @@
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" s="181"/>
+      <c r="A112" s="154"/>
       <c r="B112" s="36"/>
       <c r="C112" s="36" t="s">
         <v>162</v>
@@ -9678,7 +9677,7 @@
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="181"/>
+      <c r="A113" s="154"/>
       <c r="B113" s="36"/>
       <c r="C113" s="36" t="s">
         <v>163</v>
@@ -9721,7 +9720,7 @@
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="181"/>
+      <c r="A114" s="154"/>
       <c r="B114" s="36"/>
       <c r="C114" s="36" t="s">
         <v>164</v>
@@ -9764,7 +9763,7 @@
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="181"/>
+      <c r="A115" s="154"/>
       <c r="B115" s="36"/>
       <c r="C115" s="36" t="s">
         <v>165</v>
@@ -9807,7 +9806,7 @@
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A116" s="181"/>
+      <c r="A116" s="154"/>
       <c r="B116" s="36"/>
       <c r="C116" s="36" t="s">
         <v>166</v>
@@ -9850,7 +9849,7 @@
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A117" s="181"/>
+      <c r="A117" s="154"/>
       <c r="B117" s="36"/>
       <c r="C117" s="36" t="s">
         <v>167</v>
@@ -9893,7 +9892,7 @@
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A118" s="181"/>
+      <c r="A118" s="154"/>
       <c r="B118" s="36"/>
       <c r="C118" s="36" t="s">
         <v>168</v>
@@ -9936,7 +9935,7 @@
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A119" s="181"/>
+      <c r="A119" s="154"/>
       <c r="B119" s="36"/>
       <c r="C119" s="36" t="s">
         <v>169</v>
@@ -9979,7 +9978,7 @@
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A120" s="181"/>
+      <c r="A120" s="154"/>
       <c r="B120" s="36"/>
       <c r="C120" s="36" t="s">
         <v>170</v>
@@ -10022,7 +10021,7 @@
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A121" s="181"/>
+      <c r="A121" s="154"/>
       <c r="B121" s="36"/>
       <c r="C121" s="36" t="s">
         <v>171</v>
@@ -10065,7 +10064,7 @@
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A122" s="181"/>
+      <c r="A122" s="154"/>
       <c r="B122" s="36"/>
       <c r="C122" s="36" t="s">
         <v>172</v>
@@ -10108,7 +10107,7 @@
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A123" s="181" t="s">
+      <c r="A123" s="154" t="s">
         <v>29</v>
       </c>
       <c r="B123" s="36"/>
@@ -10156,7 +10155,7 @@
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A124" s="181" t="s">
+      <c r="A124" s="154" t="s">
         <v>29</v>
       </c>
       <c r="B124" s="36"/>
@@ -10267,30 +10266,30 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C128" s="163"/>
-      <c r="D128" s="163"/>
-      <c r="E128" s="163"/>
-      <c r="F128" s="163"/>
-      <c r="G128" s="163"/>
-      <c r="H128" s="163"/>
-      <c r="I128" s="163"/>
-      <c r="J128" s="163"/>
-      <c r="K128" s="163"/>
-      <c r="L128" s="163"/>
-      <c r="M128" s="163"/>
+      <c r="C128" s="176"/>
+      <c r="D128" s="176"/>
+      <c r="E128" s="176"/>
+      <c r="F128" s="176"/>
+      <c r="G128" s="176"/>
+      <c r="H128" s="176"/>
+      <c r="I128" s="176"/>
+      <c r="J128" s="176"/>
+      <c r="K128" s="176"/>
+      <c r="L128" s="176"/>
+      <c r="M128" s="176"/>
     </row>
     <row r="129" spans="3:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="163"/>
-      <c r="D129" s="163"/>
-      <c r="E129" s="163"/>
-      <c r="F129" s="163"/>
-      <c r="G129" s="163"/>
-      <c r="H129" s="163"/>
-      <c r="I129" s="163"/>
-      <c r="J129" s="163"/>
-      <c r="K129" s="163"/>
-      <c r="L129" s="163"/>
-      <c r="M129" s="163"/>
+      <c r="C129" s="176"/>
+      <c r="D129" s="176"/>
+      <c r="E129" s="176"/>
+      <c r="F129" s="176"/>
+      <c r="G129" s="176"/>
+      <c r="H129" s="176"/>
+      <c r="I129" s="176"/>
+      <c r="J129" s="176"/>
+      <c r="K129" s="176"/>
+      <c r="L129" s="176"/>
+      <c r="M129" s="176"/>
     </row>
     <row r="130" spans="3:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="88"/>
@@ -10306,110 +10305,110 @@
       <c r="M130" s="88"/>
     </row>
     <row r="131" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C131" s="163" t="s">
+      <c r="C131" s="176" t="s">
         <v>296</v>
       </c>
-      <c r="D131" s="163"/>
-      <c r="E131" s="163"/>
-      <c r="F131" s="163"/>
-      <c r="G131" s="163"/>
-      <c r="H131" s="163"/>
-      <c r="I131" s="163"/>
-      <c r="J131" s="163"/>
-      <c r="K131" s="163"/>
-      <c r="L131" s="163"/>
-      <c r="M131" s="163"/>
+      <c r="D131" s="176"/>
+      <c r="E131" s="176"/>
+      <c r="F131" s="176"/>
+      <c r="G131" s="176"/>
+      <c r="H131" s="176"/>
+      <c r="I131" s="176"/>
+      <c r="J131" s="176"/>
+      <c r="K131" s="176"/>
+      <c r="L131" s="176"/>
+      <c r="M131" s="176"/>
     </row>
     <row r="132" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C132" s="163"/>
-      <c r="D132" s="163"/>
-      <c r="E132" s="163"/>
-      <c r="F132" s="163"/>
-      <c r="G132" s="163"/>
-      <c r="H132" s="163"/>
-      <c r="I132" s="163"/>
-      <c r="J132" s="163"/>
-      <c r="K132" s="163"/>
-      <c r="L132" s="163"/>
-      <c r="M132" s="163"/>
+      <c r="C132" s="176"/>
+      <c r="D132" s="176"/>
+      <c r="E132" s="176"/>
+      <c r="F132" s="176"/>
+      <c r="G132" s="176"/>
+      <c r="H132" s="176"/>
+      <c r="I132" s="176"/>
+      <c r="J132" s="176"/>
+      <c r="K132" s="176"/>
+      <c r="L132" s="176"/>
+      <c r="M132" s="176"/>
     </row>
     <row r="133" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C133" s="163"/>
-      <c r="D133" s="163"/>
-      <c r="E133" s="163"/>
-      <c r="F133" s="163"/>
-      <c r="G133" s="163"/>
-      <c r="H133" s="163"/>
-      <c r="I133" s="163"/>
-      <c r="J133" s="163"/>
-      <c r="K133" s="163"/>
-      <c r="L133" s="163"/>
-      <c r="M133" s="163"/>
+      <c r="C133" s="176"/>
+      <c r="D133" s="176"/>
+      <c r="E133" s="176"/>
+      <c r="F133" s="176"/>
+      <c r="G133" s="176"/>
+      <c r="H133" s="176"/>
+      <c r="I133" s="176"/>
+      <c r="J133" s="176"/>
+      <c r="K133" s="176"/>
+      <c r="L133" s="176"/>
+      <c r="M133" s="176"/>
     </row>
     <row r="134" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C134" s="163"/>
-      <c r="D134" s="163"/>
-      <c r="E134" s="163"/>
-      <c r="F134" s="163"/>
-      <c r="G134" s="163"/>
-      <c r="H134" s="163"/>
-      <c r="I134" s="163"/>
-      <c r="J134" s="163"/>
-      <c r="K134" s="163"/>
-      <c r="L134" s="163"/>
-      <c r="M134" s="163"/>
+      <c r="C134" s="176"/>
+      <c r="D134" s="176"/>
+      <c r="E134" s="176"/>
+      <c r="F134" s="176"/>
+      <c r="G134" s="176"/>
+      <c r="H134" s="176"/>
+      <c r="I134" s="176"/>
+      <c r="J134" s="176"/>
+      <c r="K134" s="176"/>
+      <c r="L134" s="176"/>
+      <c r="M134" s="176"/>
     </row>
     <row r="135" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C135" s="163"/>
-      <c r="D135" s="163"/>
-      <c r="E135" s="163"/>
-      <c r="F135" s="163"/>
-      <c r="G135" s="163"/>
-      <c r="H135" s="163"/>
-      <c r="I135" s="163"/>
-      <c r="J135" s="163"/>
-      <c r="K135" s="163"/>
-      <c r="L135" s="163"/>
-      <c r="M135" s="163"/>
+      <c r="C135" s="176"/>
+      <c r="D135" s="176"/>
+      <c r="E135" s="176"/>
+      <c r="F135" s="176"/>
+      <c r="G135" s="176"/>
+      <c r="H135" s="176"/>
+      <c r="I135" s="176"/>
+      <c r="J135" s="176"/>
+      <c r="K135" s="176"/>
+      <c r="L135" s="176"/>
+      <c r="M135" s="176"/>
     </row>
     <row r="136" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C136" s="163"/>
-      <c r="D136" s="163"/>
-      <c r="E136" s="163"/>
-      <c r="F136" s="163"/>
-      <c r="G136" s="163"/>
-      <c r="H136" s="163"/>
-      <c r="I136" s="163"/>
-      <c r="J136" s="163"/>
-      <c r="K136" s="163"/>
-      <c r="L136" s="163"/>
-      <c r="M136" s="163"/>
+      <c r="C136" s="176"/>
+      <c r="D136" s="176"/>
+      <c r="E136" s="176"/>
+      <c r="F136" s="176"/>
+      <c r="G136" s="176"/>
+      <c r="H136" s="176"/>
+      <c r="I136" s="176"/>
+      <c r="J136" s="176"/>
+      <c r="K136" s="176"/>
+      <c r="L136" s="176"/>
+      <c r="M136" s="176"/>
     </row>
     <row r="137" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C137" s="163"/>
-      <c r="D137" s="163"/>
-      <c r="E137" s="163"/>
-      <c r="F137" s="163"/>
-      <c r="G137" s="163"/>
-      <c r="H137" s="163"/>
-      <c r="I137" s="163"/>
-      <c r="J137" s="163"/>
-      <c r="K137" s="163"/>
-      <c r="L137" s="163"/>
-      <c r="M137" s="163"/>
+      <c r="C137" s="176"/>
+      <c r="D137" s="176"/>
+      <c r="E137" s="176"/>
+      <c r="F137" s="176"/>
+      <c r="G137" s="176"/>
+      <c r="H137" s="176"/>
+      <c r="I137" s="176"/>
+      <c r="J137" s="176"/>
+      <c r="K137" s="176"/>
+      <c r="L137" s="176"/>
+      <c r="M137" s="176"/>
     </row>
     <row r="138" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C138" s="163"/>
-      <c r="D138" s="163"/>
-      <c r="E138" s="163"/>
-      <c r="F138" s="163"/>
-      <c r="G138" s="163"/>
-      <c r="H138" s="163"/>
-      <c r="I138" s="163"/>
-      <c r="J138" s="163"/>
-      <c r="K138" s="163"/>
-      <c r="L138" s="163"/>
-      <c r="M138" s="163"/>
+      <c r="C138" s="176"/>
+      <c r="D138" s="176"/>
+      <c r="E138" s="176"/>
+      <c r="F138" s="176"/>
+      <c r="G138" s="176"/>
+      <c r="H138" s="176"/>
+      <c r="I138" s="176"/>
+      <c r="J138" s="176"/>
+      <c r="K138" s="176"/>
+      <c r="L138" s="176"/>
+      <c r="M138" s="176"/>
     </row>
     <row r="139" spans="3:15" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C139" s="88"/>
@@ -10438,109 +10437,104 @@
       <c r="M140" s="88"/>
     </row>
     <row r="141" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C141" s="182" t="s">
+      <c r="C141" s="175" t="s">
         <v>295</v>
       </c>
-      <c r="D141" s="182"/>
-      <c r="E141" s="182"/>
-      <c r="F141" s="182"/>
-      <c r="G141" s="182"/>
-      <c r="H141" s="182"/>
-      <c r="I141" s="182"/>
-      <c r="J141" s="182"/>
-      <c r="K141" s="182"/>
-      <c r="L141" s="182"/>
-      <c r="M141" s="182"/>
+      <c r="D141" s="175"/>
+      <c r="E141" s="175"/>
+      <c r="F141" s="175"/>
+      <c r="G141" s="175"/>
+      <c r="H141" s="175"/>
+      <c r="I141" s="175"/>
+      <c r="J141" s="175"/>
+      <c r="K141" s="175"/>
+      <c r="L141" s="175"/>
+      <c r="M141" s="175"/>
     </row>
     <row r="142" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C142" s="182"/>
-      <c r="D142" s="182"/>
-      <c r="E142" s="182"/>
-      <c r="F142" s="182"/>
-      <c r="G142" s="182"/>
-      <c r="H142" s="182"/>
-      <c r="I142" s="182"/>
-      <c r="J142" s="182"/>
-      <c r="K142" s="182"/>
-      <c r="L142" s="182"/>
-      <c r="M142" s="182"/>
+      <c r="C142" s="175"/>
+      <c r="D142" s="175"/>
+      <c r="E142" s="175"/>
+      <c r="F142" s="175"/>
+      <c r="G142" s="175"/>
+      <c r="H142" s="175"/>
+      <c r="I142" s="175"/>
+      <c r="J142" s="175"/>
+      <c r="K142" s="175"/>
+      <c r="L142" s="175"/>
+      <c r="M142" s="175"/>
     </row>
     <row r="143" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C143" s="182"/>
-      <c r="D143" s="182"/>
-      <c r="E143" s="182"/>
-      <c r="F143" s="182"/>
-      <c r="G143" s="182"/>
-      <c r="H143" s="182"/>
-      <c r="I143" s="182"/>
-      <c r="J143" s="182"/>
-      <c r="K143" s="182"/>
-      <c r="L143" s="182"/>
-      <c r="M143" s="182"/>
+      <c r="C143" s="175"/>
+      <c r="D143" s="175"/>
+      <c r="E143" s="175"/>
+      <c r="F143" s="175"/>
+      <c r="G143" s="175"/>
+      <c r="H143" s="175"/>
+      <c r="I143" s="175"/>
+      <c r="J143" s="175"/>
+      <c r="K143" s="175"/>
+      <c r="L143" s="175"/>
+      <c r="M143" s="175"/>
       <c r="O143" s="96">
         <f>K1-J126</f>
         <v>-1447047.6731600082</v>
       </c>
     </row>
     <row r="144" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C144" s="182"/>
-      <c r="D144" s="182"/>
-      <c r="E144" s="182"/>
-      <c r="F144" s="182"/>
-      <c r="G144" s="182"/>
-      <c r="H144" s="182"/>
-      <c r="I144" s="182"/>
-      <c r="J144" s="182"/>
-      <c r="K144" s="182"/>
-      <c r="L144" s="182"/>
-      <c r="M144" s="182"/>
+      <c r="C144" s="175"/>
+      <c r="D144" s="175"/>
+      <c r="E144" s="175"/>
+      <c r="F144" s="175"/>
+      <c r="G144" s="175"/>
+      <c r="H144" s="175"/>
+      <c r="I144" s="175"/>
+      <c r="J144" s="175"/>
+      <c r="K144" s="175"/>
+      <c r="L144" s="175"/>
+      <c r="M144" s="175"/>
     </row>
     <row r="145" spans="3:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="182"/>
-      <c r="D145" s="182"/>
-      <c r="E145" s="182"/>
-      <c r="F145" s="182"/>
-      <c r="G145" s="182"/>
-      <c r="H145" s="182"/>
-      <c r="I145" s="182"/>
-      <c r="J145" s="182"/>
-      <c r="K145" s="182"/>
-      <c r="L145" s="182"/>
-      <c r="M145" s="182"/>
+      <c r="C145" s="175"/>
+      <c r="D145" s="175"/>
+      <c r="E145" s="175"/>
+      <c r="F145" s="175"/>
+      <c r="G145" s="175"/>
+      <c r="H145" s="175"/>
+      <c r="I145" s="175"/>
+      <c r="J145" s="175"/>
+      <c r="K145" s="175"/>
+      <c r="L145" s="175"/>
+      <c r="M145" s="175"/>
     </row>
     <row r="146" spans="3:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="182"/>
-      <c r="D146" s="182"/>
-      <c r="E146" s="182"/>
-      <c r="F146" s="182"/>
-      <c r="G146" s="182"/>
-      <c r="H146" s="182"/>
-      <c r="I146" s="182"/>
-      <c r="J146" s="182"/>
-      <c r="K146" s="182"/>
-      <c r="L146" s="182"/>
-      <c r="M146" s="182"/>
+      <c r="C146" s="175"/>
+      <c r="D146" s="175"/>
+      <c r="E146" s="175"/>
+      <c r="F146" s="175"/>
+      <c r="G146" s="175"/>
+      <c r="H146" s="175"/>
+      <c r="I146" s="175"/>
+      <c r="J146" s="175"/>
+      <c r="K146" s="175"/>
+      <c r="L146" s="175"/>
+      <c r="M146" s="175"/>
     </row>
     <row r="147" spans="3:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="182"/>
-      <c r="D147" s="182"/>
-      <c r="E147" s="182"/>
-      <c r="F147" s="182"/>
-      <c r="G147" s="182"/>
-      <c r="H147" s="182"/>
-      <c r="I147" s="182"/>
-      <c r="J147" s="182"/>
-      <c r="K147" s="182"/>
-      <c r="L147" s="182"/>
-      <c r="M147" s="182"/>
+      <c r="C147" s="175"/>
+      <c r="D147" s="175"/>
+      <c r="E147" s="175"/>
+      <c r="F147" s="175"/>
+      <c r="G147" s="175"/>
+      <c r="H147" s="175"/>
+      <c r="I147" s="175"/>
+      <c r="J147" s="175"/>
+      <c r="K147" s="175"/>
+      <c r="L147" s="175"/>
+      <c r="M147" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P7:Q8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C141:M147"/>
@@ -10554,6 +10548,11 @@
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="C131:M138"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EL MIRADOR/Junio/JUNIO - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Junio/JUNIO - EL MIRADOR .xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B644071F-8714-42A7-B182-6DC59008D528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FDB61A-1F73-4E73-9859-E755BF35361C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
+    <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$148</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="304">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -738,9 +739,6 @@
     <t>Lobalo Lorena - Vega Maximiliano</t>
   </si>
   <si>
-    <t>PERÍODO: JUNIO</t>
-  </si>
-  <si>
     <t xml:space="preserve">SEGUROS </t>
   </si>
   <si>
@@ -808,9 +806,6 @@
   </si>
   <si>
     <t>Efect. 23/06</t>
-  </si>
-  <si>
-    <t>ADS - Abono de mantenimiento ascensores Junio del 2025</t>
   </si>
   <si>
     <t>Transf 25/06</t>
@@ -935,6 +930,15 @@
   <si>
     <t xml:space="preserve">MAIL: elmiradorconsorcios@gmail.com
 </t>
+  </si>
+  <si>
+    <t>PERÍODO: JULIO</t>
+  </si>
+  <si>
+    <t>ADS - Abono de mantenimiento ascensores JULIO del 2025</t>
+  </si>
+  <si>
+    <t>AGREGAR MAILS DEL FOLEO</t>
   </si>
 </sst>
 </file>
@@ -942,13 +946,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1496,11 +1500,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1509,7 +1513,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1517,96 +1521,96 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1615,20 +1619,20 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1637,8 +1641,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1652,12 +1656,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1677,7 +1681,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1689,14 +1693,14 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1729,26 +1733,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1756,10 +1748,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1783,6 +1775,21 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2207,27 +2214,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="131"/>
       <c r="B1" s="144"/>
       <c r="C1" s="156" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D1" s="156"/>
       <c r="E1" s="157"/>
@@ -2237,11 +2244,11 @@
       <c r="I1" s="129"/>
       <c r="J1" s="130"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="132"/>
       <c r="B2" s="145"/>
       <c r="C2" s="145" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D2" s="145"/>
       <c r="E2" s="146"/>
@@ -2251,15 +2258,15 @@
       <c r="I2" s="146"/>
       <c r="J2" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="132"/>
       <c r="B3" s="145"/>
       <c r="C3" s="145" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D3" s="145"/>
       <c r="E3" s="145" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F3" s="146"/>
       <c r="G3" s="146"/>
@@ -2267,11 +2274,11 @@
       <c r="I3" s="146"/>
       <c r="J3" s="128"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="132"/>
       <c r="B4" s="145"/>
       <c r="C4" s="145" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D4" s="146"/>
       <c r="E4" s="146"/>
@@ -2281,15 +2288,15 @@
       <c r="I4" s="146"/>
       <c r="J4" s="128"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="140"/>
       <c r="B5" s="145"/>
       <c r="C5" s="145" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="D5" s="145"/>
       <c r="E5" s="145" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F5" s="145"/>
       <c r="G5" s="145"/>
@@ -2297,7 +2304,7 @@
       <c r="I5" s="145"/>
       <c r="J5" s="141"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="140"/>
       <c r="B6" s="145"/>
       <c r="C6" s="145" t="s">
@@ -2311,7 +2318,7 @@
       <c r="I6" s="145"/>
       <c r="J6" s="141"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="142"/>
       <c r="B7" s="143"/>
       <c r="C7" s="143"/>
@@ -2323,13 +2330,13 @@
       <c r="I7" s="143"/>
       <c r="J7" s="147"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="158" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B14" s="158"/>
       <c r="C14" s="158"/>
@@ -2341,7 +2348,7 @@
       <c r="I14" s="158"/>
       <c r="J14" s="158"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="158"/>
       <c r="B15" s="158"/>
       <c r="C15" s="158"/>
@@ -2353,7 +2360,7 @@
       <c r="I15" s="158"/>
       <c r="J15" s="158"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="158"/>
       <c r="B16" s="158"/>
       <c r="C16" s="158"/>
@@ -2365,7 +2372,7 @@
       <c r="I16" s="158"/>
       <c r="J16" s="158"/>
     </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="158"/>
       <c r="B17" s="158"/>
       <c r="C17" s="158"/>
@@ -2377,7 +2384,7 @@
       <c r="I17" s="158"/>
       <c r="J17" s="158"/>
     </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="158"/>
       <c r="B18" s="158"/>
       <c r="C18" s="158"/>
@@ -2389,14 +2396,14 @@
       <c r="I18" s="158"/>
       <c r="J18" s="158"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="113"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H20" s="113"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
         <v>22</v>
       </c>
@@ -2422,9 +2429,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -2436,7 +2443,7 @@
       <c r="I22" s="114"/>
       <c r="J22" s="114"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>48</v>
       </c>
@@ -2453,9 +2460,9 @@
       <c r="I23" s="63"/>
       <c r="J23" s="63"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2469,9 +2476,9 @@
       <c r="I24" s="63"/>
       <c r="J24" s="63"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -2485,9 +2492,9 @@
       <c r="I25" s="63"/>
       <c r="J25" s="63"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2501,9 +2508,9 @@
       <c r="I26" s="63"/>
       <c r="J26" s="63"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2517,7 +2524,7 @@
       <c r="I27" s="63"/>
       <c r="J27" s="63"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
@@ -2533,7 +2540,7 @@
       <c r="I28" s="63"/>
       <c r="J28" s="63"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="112" t="s">
         <v>175</v>
       </c>
@@ -2550,9 +2557,9 @@
       <c r="I29" s="111"/>
       <c r="J29" s="111"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2564,7 +2571,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>48</v>
       </c>
@@ -2581,9 +2588,9 @@
       <c r="I31" s="63"/>
       <c r="J31" s="63"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2597,9 +2604,9 @@
       <c r="I32" s="63"/>
       <c r="J32" s="63"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -2613,9 +2620,9 @@
       <c r="I33" s="63"/>
       <c r="J33" s="63"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -2629,9 +2636,9 @@
       <c r="I34" s="63"/>
       <c r="J34" s="63"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -2645,7 +2652,7 @@
       <c r="I35" s="63"/>
       <c r="J35" s="63"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="112" t="s">
         <v>175</v>
       </c>
@@ -2662,7 +2669,7 @@
       <c r="I36" s="111"/>
       <c r="J36" s="111"/>
     </row>
-    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="34" t="s">
         <v>1</v>
       </c>
@@ -2705,7 +2712,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>37</v>
       </c>
@@ -2728,7 +2735,7 @@
       </c>
       <c r="L38" s="75"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2749,7 +2756,7 @@
       </c>
       <c r="L39" s="75"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -2762,7 +2769,7 @@
       <c r="J40" s="6"/>
       <c r="L40" s="75"/>
     </row>
-    <row r="41" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2775,7 +2782,7 @@
       <c r="J41" s="6"/>
       <c r="L41" s="75"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="34" t="s">
         <v>43</v>
       </c>
@@ -2806,9 +2813,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2827,13 +2834,13 @@
       </c>
       <c r="L43" s="75"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D44" s="97">
         <v>79500.009999999995</v>
@@ -2849,7 +2856,7 @@
       <c r="J44" s="63"/>
       <c r="L44" s="75"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="33"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2868,7 +2875,7 @@
       </c>
       <c r="L45" s="75"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="34" t="s">
         <v>38</v>
       </c>
@@ -2896,9 +2903,9 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B47" s="36"/>
       <c r="C47" s="36"/>
@@ -2911,13 +2918,13 @@
       <c r="J47" s="50"/>
       <c r="L47" s="75"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="36" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B48" s="36"/>
       <c r="C48" s="36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D48" s="97">
         <v>132512.6</v>
@@ -2930,16 +2937,16 @@
       <c r="J48" s="50"/>
       <c r="L48" s="75"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B49" s="36"/>
       <c r="C49" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D49" s="97">
-        <v>660181</v>
+        <v>669159</v>
       </c>
       <c r="E49" s="50"/>
       <c r="F49" s="50"/>
@@ -2949,16 +2956,16 @@
       <c r="J49" s="50"/>
       <c r="L49" s="75"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="36" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B50" s="36"/>
       <c r="C50" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="D50" s="97">
-        <v>589447</v>
+        <v>269</v>
+      </c>
+      <c r="D50" s="187">
+        <v>643422</v>
       </c>
       <c r="E50" s="50"/>
       <c r="F50" s="50"/>
@@ -2968,50 +2975,50 @@
       <c r="J50" s="50"/>
       <c r="L50" s="75"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="34" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
       <c r="D51" s="150">
         <f>SUM(D48:D50)</f>
-        <v>1382140.6</v>
+        <v>1445093.6</v>
       </c>
       <c r="E51" s="43">
         <f>D51*93.2%</f>
-        <v>1288155.0392000002</v>
+        <v>1346827.2352000002</v>
       </c>
       <c r="F51" s="89">
         <f>$D51*1.08%</f>
-        <v>14927.118480000001</v>
+        <v>15607.010880000002</v>
       </c>
       <c r="G51" s="89">
         <f>$D51*1.28%</f>
-        <v>17691.399680000002</v>
+        <v>18497.198080000002</v>
       </c>
       <c r="H51" s="89">
         <f>$D51*1.21%</f>
-        <v>16723.901260000002</v>
+        <v>17485.632560000002</v>
       </c>
       <c r="I51" s="89">
         <f>$D51*1.49%</f>
-        <v>20593.894940000002</v>
+        <v>21531.894640000002</v>
       </c>
       <c r="J51" s="89">
         <f>D51*1.74%</f>
-        <v>24049.246439999999</v>
+        <v>25144.628639999999</v>
       </c>
       <c r="K51" s="44">
         <f>E51+J51+F51+G51+H51+I51</f>
-        <v>1382140.6</v>
+        <v>1445093.6000000003</v>
       </c>
       <c r="L51" s="75" t="str">
         <f>IF(D51=K51, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="33" t="s">
         <v>2</v>
       </c>
@@ -3026,9 +3033,9 @@
       <c r="J52" s="6"/>
       <c r="L52" s="75"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -3043,7 +3050,7 @@
       <c r="J53" s="6"/>
       <c r="L53" s="75"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -3056,9 +3063,9 @@
       <c r="J54" s="6"/>
       <c r="L54" s="75"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B55" s="34"/>
       <c r="C55" s="34"/>
@@ -3099,9 +3106,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -3114,15 +3121,15 @@
       <c r="J56" s="37"/>
       <c r="L56" s="75"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D57" s="45">
+        <v>242</v>
+      </c>
+      <c r="D57" s="188">
         <v>160913</v>
       </c>
       <c r="E57" s="63">
@@ -3155,15 +3162,15 @@
       </c>
       <c r="L57" s="75"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="D58" s="45">
+        <v>244</v>
+      </c>
+      <c r="D58" s="188">
         <v>7907</v>
       </c>
       <c r="E58" s="63">
@@ -3196,15 +3203,15 @@
       </c>
       <c r="L58" s="75"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="D59" s="45">
+        <v>246</v>
+      </c>
+      <c r="D59" s="188">
         <v>7907</v>
       </c>
       <c r="E59" s="63">
@@ -3237,7 +3244,7 @@
       </c>
       <c r="L59" s="75"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="34" t="s">
         <v>3</v>
       </c>
@@ -3280,7 +3287,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="33" t="s">
         <v>4</v>
       </c>
@@ -3295,13 +3302,13 @@
       <c r="J61" s="6"/>
       <c r="L61" s="75"/>
     </row>
-    <row r="62" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="80" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D62" s="152">
         <v>27920.59</v>
@@ -3347,48 +3354,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D63" s="152">
-        <v>164905.93</v>
+        <v>257</v>
+      </c>
+      <c r="D63" s="186">
+        <v>1233986.03</v>
       </c>
       <c r="E63" s="74">
         <f>D63*93.2%</f>
-        <v>153692.32676</v>
+        <v>1150074.9799600001</v>
       </c>
       <c r="F63" s="63">
         <f>$D63*1.08%</f>
-        <v>1780.984044</v>
+        <v>13327.049124000001</v>
       </c>
       <c r="G63" s="63">
         <f>$D63*1.28%</f>
-        <v>2110.7959040000001</v>
+        <v>15795.021184000001</v>
       </c>
       <c r="H63" s="63">
         <f>$D63*1.21%</f>
-        <v>1995.3617529999999</v>
+        <v>14931.230963</v>
       </c>
       <c r="I63" s="63">
         <f>$D63*1.49%</f>
-        <v>2457.0983569999999</v>
+        <v>18386.391846999999</v>
       </c>
       <c r="J63" s="63">
         <f>D63*1.74%</f>
-        <v>2869.3631819999996</v>
+        <v>21471.356921999999</v>
       </c>
       <c r="K63" s="44">
         <f t="shared" ref="K63:K69" si="7">D63</f>
-        <v>164905.93</v>
+        <v>1233986.03</v>
       </c>
       <c r="L63" s="84">
         <f>E63+J63+I63+H63+G63+F63</f>
-        <v>164905.93000000002</v>
+        <v>1233986.03</v>
       </c>
       <c r="M63" s="96">
         <f>L63-D63</f>
@@ -3399,13 +3406,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D64" s="45">
         <v>96208.3</v>
@@ -3436,13 +3443,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D65" s="45">
         <v>149126.03</v>
@@ -3467,9 +3474,9 @@
       <c r="M65" s="96"/>
       <c r="N65" s="96"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="36" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B66" s="36"/>
       <c r="C66" s="36"/>
@@ -3502,9 +3509,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="36" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B67" s="36"/>
       <c r="C67" s="36"/>
@@ -3532,9 +3539,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="80" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B68" s="137"/>
       <c r="C68" s="137"/>
@@ -3565,7 +3572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="134"/>
       <c r="B69" s="135"/>
       <c r="C69" s="136"/>
@@ -3596,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="80"/>
       <c r="B70" s="81"/>
       <c r="C70" s="81"/>
@@ -3614,7 +3621,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="34" t="s">
         <v>5</v>
       </c>
@@ -3622,35 +3629,35 @@
       <c r="C71" s="35"/>
       <c r="D71" s="43">
         <f>SUM(D62:D70)</f>
-        <v>468160.85</v>
+        <v>1537240.9500000002</v>
       </c>
       <c r="E71" s="43">
         <f>SUM(E62:E70)</f>
-        <v>455048.64664000005</v>
+        <v>1451431.2998400002</v>
       </c>
       <c r="F71" s="43">
         <f t="shared" ref="F71:I71" si="10">SUM(F62:F70)</f>
-        <v>2082.5264160000002</v>
+        <v>13628.591496000001</v>
       </c>
       <c r="G71" s="43">
         <f t="shared" si="10"/>
-        <v>2468.1794559999998</v>
+        <v>16152.404736</v>
       </c>
       <c r="H71" s="43">
         <f t="shared" si="10"/>
-        <v>2333.2008919999998</v>
+        <v>15269.070102</v>
       </c>
       <c r="I71" s="43">
         <f t="shared" si="10"/>
-        <v>2873.1151479999999</v>
+        <v>18802.408638000001</v>
       </c>
       <c r="J71" s="43">
         <f>SUM(J62:J70)</f>
-        <v>3355.1814479999994</v>
+        <v>21957.175187999997</v>
       </c>
       <c r="K71" s="44">
         <f>E71+J71+F71+G71+H71+I71</f>
-        <v>468160.85000000003</v>
+        <v>1537240.9500000004</v>
       </c>
       <c r="L71" s="75" t="str">
         <f>IF(D71=K71, "", "Error")</f>
@@ -3661,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -3674,7 +3681,7 @@
       <c r="J72" s="6"/>
       <c r="L72" s="75"/>
     </row>
-    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -3687,9 +3694,9 @@
       <c r="J73" s="6"/>
       <c r="L73" s="75"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -3702,12 +3709,12 @@
       <c r="J74" s="6"/>
       <c r="L74" s="75"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="45"/>
@@ -3738,9 +3745,9 @@
       <c r="K75" s="83"/>
       <c r="L75" s="75"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B76" s="36"/>
       <c r="C76" s="6"/>
@@ -3774,9 +3781,9 @@
       <c r="K76" s="83"/>
       <c r="L76" s="75"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B77" s="36"/>
       <c r="C77" s="6"/>
@@ -3795,9 +3802,9 @@
       <c r="K77" s="83"/>
       <c r="L77" s="75"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="6"/>
@@ -3831,9 +3838,9 @@
       <c r="K78" s="83"/>
       <c r="L78" s="75"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="6"/>
@@ -3867,9 +3874,9 @@
       <c r="K79" s="83"/>
       <c r="L79" s="75"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B80" s="36"/>
       <c r="C80" s="6"/>
@@ -3888,9 +3895,9 @@
       <c r="K80" s="83"/>
       <c r="L80" s="75"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -3925,9 +3932,9 @@
       <c r="L81" s="75"/>
       <c r="M81" s="44"/>
     </row>
-    <row r="82" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="34" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B82" s="34"/>
       <c r="C82" s="34"/>
@@ -3969,7 +3976,7 @@
       </c>
       <c r="N82" s="44"/>
     </row>
-    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -3982,7 +3989,7 @@
       <c r="J83" s="6"/>
       <c r="L83" s="75"/>
     </row>
-    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -3995,7 +4002,7 @@
       <c r="J84" s="6"/>
       <c r="L84" s="75"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>6</v>
       </c>
@@ -4010,7 +4017,7 @@
       <c r="J85" s="6"/>
       <c r="L85" s="75"/>
     </row>
-    <row r="86" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>7</v>
       </c>
@@ -4047,7 +4054,7 @@
       </c>
       <c r="L86" s="75"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="33"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -4061,7 +4068,7 @@
       <c r="L87" s="75"/>
       <c r="N87" s="45"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -4075,7 +4082,7 @@
       <c r="L88" s="75"/>
       <c r="N88" s="44"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="34" t="s">
         <v>8</v>
       </c>
@@ -4119,7 +4126,7 @@
       </c>
       <c r="N89" s="44"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>31</v>
       </c>
@@ -4152,7 +4159,7 @@
       </c>
       <c r="L90" s="75"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>32</v>
       </c>
@@ -4185,9 +4192,9 @@
       </c>
       <c r="L91" s="75"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B92" s="34"/>
       <c r="C92" s="34"/>
@@ -4228,7 +4235,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="117"/>
       <c r="B93" s="117"/>
       <c r="C93" s="117"/>
@@ -4241,7 +4248,7 @@
       <c r="J93" s="117"/>
       <c r="L93" s="75"/>
     </row>
-    <row r="94" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="119" t="s">
         <v>49</v>
       </c>
@@ -4283,7 +4290,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="122"/>
       <c r="B95" s="123"/>
       <c r="C95" s="123"/>
@@ -4297,7 +4304,7 @@
       <c r="K95" s="44"/>
       <c r="L95" s="75"/>
     </row>
-    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>33</v>
       </c>
@@ -4305,35 +4312,35 @@
       <c r="C96" s="4"/>
       <c r="D96" s="101">
         <f>SUM(D94+D51+D46+D92+D89+D82+D71+D60+D42+D37+D55)</f>
-        <v>7142595.8599999994</v>
+        <v>8274628.959999999</v>
       </c>
       <c r="E96" s="101">
         <f t="shared" ref="E96" si="15">SUM(E94+E51+E46+E92+E89+E82+E71+E60+E42+E37+E55)</f>
-        <v>6729566.4766400009</v>
+        <v>7784621.325840001</v>
       </c>
       <c r="F96" s="101">
         <f>SUM(F94+F51+F46+F92+F89+F82+F71+F60+F42+F37+F55)</f>
-        <v>65598.78441600001</v>
+        <v>77824.741896000007</v>
       </c>
       <c r="G96" s="101">
         <f>SUM(G94+G51+G46+G92+G89+G82+G71+G60+G42+G37+G55)</f>
-        <v>77746.707456000004</v>
+        <v>92236.731136000002</v>
       </c>
       <c r="H96" s="101">
         <f>SUM(H94+H51+H46+H92+H89+H82+H71+H60+H42+H37+H55)</f>
-        <v>73494.934391999996</v>
+        <v>87192.534901999999</v>
       </c>
       <c r="I96" s="101">
         <f>SUM(I94+I51+I46+I92+I89+I82+I71+I60+I42+I37+I55)</f>
-        <v>90502.026647999999</v>
+        <v>107369.319838</v>
       </c>
       <c r="J96" s="101">
         <f>SUM(J94+J51+J46+J92+J89+J82+J71+J60+J42+J37+J55)</f>
-        <v>105686.93044799998</v>
+        <v>125384.30638799998</v>
       </c>
       <c r="K96" s="44">
         <f>E96+J96+F96+G96+H96+I96</f>
-        <v>7142595.8600000013</v>
+        <v>8274628.9600000009</v>
       </c>
       <c r="L96" s="75" t="str">
         <f>IF(D96=K96, "", "Error")</f>
@@ -4344,7 +4351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D97" s="99"/>
       <c r="E97" s="44"/>
       <c r="F97" s="44"/>
@@ -4352,7 +4359,7 @@
       <c r="H97" s="44"/>
       <c r="I97" s="44"/>
     </row>
-    <row r="98" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="70" t="s">
         <v>44</v>
       </c>
@@ -4364,9 +4371,9 @@
       <c r="H98" s="44"/>
       <c r="I98" s="44"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C99" s="155">
         <f>90000-9000</f>
@@ -4378,7 +4385,7 @@
       <c r="H99" s="44"/>
       <c r="I99" s="44"/>
     </row>
-    <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="C100" s="67"/>
       <c r="E100" s="44"/>
@@ -4387,7 +4394,7 @@
       <c r="H100" s="44"/>
       <c r="I100" s="44"/>
     </row>
-    <row r="101" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="71" t="s">
         <v>18</v>
       </c>
@@ -4402,21 +4409,21 @@
       <c r="H101" s="44"/>
       <c r="I101" s="44"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E102" s="44"/>
       <c r="F102" s="44"/>
       <c r="G102" s="44"/>
       <c r="H102" s="44"/>
       <c r="I102" s="44"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E103" s="65"/>
       <c r="F103" s="65"/>
       <c r="G103" s="65"/>
       <c r="H103" s="65"/>
       <c r="I103" s="65"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="164" t="s">
         <v>39</v>
       </c>
@@ -4442,7 +4449,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="166"/>
       <c r="B105" s="167"/>
       <c r="C105" s="93"/>
@@ -4457,7 +4464,7 @@
       <c r="I105" s="74"/>
       <c r="J105" s="63"/>
     </row>
-    <row r="106" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="166"/>
       <c r="B106" s="167"/>
       <c r="C106" s="93"/>
@@ -4469,7 +4476,7 @@
       <c r="I106" s="74"/>
       <c r="J106" s="63"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="161" t="s">
         <v>18</v>
       </c>
@@ -4500,32 +4507,32 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E109" s="44"/>
       <c r="F109" s="44"/>
       <c r="G109" s="44"/>
       <c r="H109" s="44"/>
       <c r="I109" s="44"/>
     </row>
-    <row r="110" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="39" t="s">
         <v>34</v>
       </c>
       <c r="B110" s="40">
         <f>D96</f>
-        <v>7142595.8599999994</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8274628.959999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B111" s="42">
         <f>D96-D94</f>
-        <v>5642595.8599999994</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+        <v>6774628.959999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D112" s="160"/>
       <c r="E112" s="160"/>
       <c r="F112" s="104"/>
@@ -4533,7 +4540,7 @@
       <c r="H112" s="104"/>
       <c r="I112" s="104"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="17" t="s">
         <v>23</v>
       </c>
@@ -4546,7 +4553,7 @@
       <c r="H113" s="104"/>
       <c r="I113" s="104"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="20" t="s">
         <v>24</v>
       </c>
@@ -4561,7 +4568,7 @@
       <c r="H114" s="104"/>
       <c r="I114" s="104"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="22" t="s">
         <v>25</v>
       </c>
@@ -4579,13 +4586,13 @@
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
         <v>41</v>
       </c>
       <c r="B116" s="95">
         <f>-B111</f>
-        <v>-5642595.8599999994</v>
+        <v>-6774628.959999999</v>
       </c>
       <c r="C116" s="19"/>
       <c r="D116" s="160"/>
@@ -4596,7 +4603,7 @@
       <c r="I116" s="104"/>
       <c r="K116" s="45"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>40</v>
       </c>
@@ -4613,7 +4620,7 @@
       <c r="I117" s="104"/>
       <c r="K117" s="55"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>35</v>
       </c>
@@ -4623,7 +4630,7 @@
       </c>
       <c r="C118" s="23"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>44</v>
       </c>
@@ -4633,27 +4640,27 @@
       </c>
       <c r="C119" s="23"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="22"/>
       <c r="B120" s="18"/>
       <c r="C120" s="23"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B121" s="24">
         <f>SUM(B114:B120)</f>
-        <v>1526404.1400000006</v>
+        <v>394371.04000000097</v>
       </c>
       <c r="C121" s="79"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="23"/>
       <c r="C122" s="19"/>
       <c r="D122" s="26"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C123" s="19"/>
       <c r="D123" s="44"/>
       <c r="E123" s="96"/>
@@ -4662,7 +4669,7 @@
       <c r="H123" s="96"/>
       <c r="I123" s="96"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="17" t="s">
         <v>28</v>
       </c>
@@ -4678,9 +4685,9 @@
       <c r="I124" s="96"/>
       <c r="J124" s="96"/>
     </row>
-    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B125" s="32"/>
       <c r="C125" s="25"/>
@@ -4691,7 +4698,7 @@
       <c r="H125" s="105"/>
       <c r="I125" s="105"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="20"/>
       <c r="B126" s="95"/>
       <c r="C126" s="25"/>
@@ -4701,7 +4708,7 @@
       <c r="H126" s="44"/>
       <c r="I126" s="44"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="37" t="s">
         <v>18</v>
       </c>
@@ -4711,18 +4718,18 @@
       </c>
       <c r="C127" s="25"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C128" s="26"/>
       <c r="D128" s="96"/>
     </row>
-    <row r="129" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B129" s="23"/>
       <c r="C129" s="19"/>
     </row>
-    <row r="131" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:18" x14ac:dyDescent="0.3">
       <c r="R131" s="10"/>
     </row>
-    <row r="134" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B134" s="159"/>
       <c r="C134" s="159"/>
       <c r="D134" s="159"/>
@@ -4732,7 +4739,7 @@
       <c r="H134" s="108"/>
       <c r="I134" s="108"/>
     </row>
-    <row r="135" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B135" s="159"/>
       <c r="C135" s="159"/>
       <c r="D135" s="159"/>
@@ -4742,7 +4749,7 @@
       <c r="H135" s="108"/>
       <c r="I135" s="108"/>
     </row>
-    <row r="136" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B136" s="159"/>
       <c r="C136" s="159"/>
       <c r="D136" s="159"/>
@@ -4752,7 +4759,7 @@
       <c r="H136" s="108"/>
       <c r="I136" s="108"/>
     </row>
-    <row r="137" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B137" s="159"/>
       <c r="C137" s="159"/>
       <c r="D137" s="159"/>
@@ -4762,7 +4769,7 @@
       <c r="H137" s="108"/>
       <c r="I137" s="108"/>
     </row>
-    <row r="138" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B138" s="159"/>
       <c r="C138" s="159"/>
       <c r="D138" s="159"/>
@@ -4791,25 +4798,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q147"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="43.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4824,15 +4831,15 @@
       <c r="J1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="177">
+      <c r="K1" s="173">
         <f>RESUMEN!D96-RESUMEN!D94</f>
-        <v>5642595.8599999994</v>
-      </c>
-      <c r="L1" s="178"/>
+        <v>6774628.959999999</v>
+      </c>
+      <c r="L1" s="174"/>
       <c r="M1" s="77"/>
       <c r="N1" s="64"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -4852,10 +4859,10 @@
       <c r="M2" s="78"/>
       <c r="N2" s="64"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="str">
         <f>RESUMEN!C5</f>
-        <v>PERÍODO: JUNIO</v>
+        <v>PERÍODO: JULIO</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -4871,7 +4878,7 @@
       <c r="M3" s="76"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4890,66 +4897,66 @@
       <c r="M4" s="54"/>
       <c r="O4" s="96">
         <f>K1-J126</f>
-        <v>-1447047.6731600082</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="168" t="s">
+        <v>-315014.57316000853</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="170" t="s">
+      <c r="B5" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="184" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="168" t="s">
+      <c r="E5" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="168" t="s">
+      <c r="F5" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="168" t="s">
+      <c r="G5" s="169" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="181" t="s">
+      <c r="H5" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="179" t="s">
+      <c r="I5" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="179" t="s">
+      <c r="J5" s="175" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="184" t="s">
+      <c r="K5" s="180" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="179" t="s">
+      <c r="L5" s="175" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="179" t="s">
+      <c r="M5" s="175" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="169"/>
-      <c r="B6" s="171"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="182"/>
-      <c r="I6" s="180"/>
-      <c r="J6" s="183"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="180"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="170"/>
+      <c r="B6" s="183"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="185"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="181"/>
+      <c r="L6" s="179"/>
+      <c r="M6" s="176"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>125</v>
       </c>
@@ -4987,12 +4994,12 @@
         <v>75258.711480960017</v>
       </c>
       <c r="N7" s="138"/>
-      <c r="P7" s="174" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q7" s="174"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P7" s="168" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q7" s="168"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
@@ -5029,10 +5036,10 @@
         <v>89195.509903359998</v>
       </c>
       <c r="N8" s="138"/>
-      <c r="P8" s="174"/>
-      <c r="Q8" s="174"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P8" s="168"/>
+      <c r="Q8" s="168"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>125</v>
       </c>
@@ -5072,14 +5079,14 @@
       </c>
       <c r="N9" s="138"/>
       <c r="P9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q9">
         <f>RESUMEN!F96</f>
-        <v>65598.78441600001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>77824.741896000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>125</v>
       </c>
@@ -5119,14 +5126,14 @@
       </c>
       <c r="N10" s="138"/>
       <c r="P10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q10">
         <f>RESUMEN!G96</f>
-        <v>77746.707456000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>92236.731136000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>125</v>
       </c>
@@ -5166,14 +5173,14 @@
       </c>
       <c r="N11" s="138"/>
       <c r="P11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q11">
         <f>RESUMEN!H96</f>
-        <v>73494.934391999996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>87192.534901999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="62" t="s">
         <v>127</v>
       </c>
@@ -5217,14 +5224,14 @@
         <v>0.01</v>
       </c>
       <c r="P12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q12">
         <f>RESUMEN!I96</f>
-        <v>90502.026647999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>107369.319838</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="62" t="s">
         <v>128</v>
       </c>
@@ -5269,14 +5276,14 @@
         <v>0.02</v>
       </c>
       <c r="P13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q13">
         <f>RESUMEN!J96</f>
-        <v>105686.93044799998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>125384.30638799998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>127</v>
       </c>
@@ -5321,7 +5328,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="62" t="s">
         <v>129</v>
       </c>
@@ -5366,7 +5373,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="62" t="s">
         <v>129</v>
       </c>
@@ -5410,7 +5417,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="62" t="s">
         <v>129</v>
       </c>
@@ -5455,7 +5462,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
         <v>127</v>
       </c>
@@ -5500,7 +5507,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>128</v>
       </c>
@@ -5545,7 +5552,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>127</v>
       </c>
@@ -5590,7 +5597,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
         <v>129</v>
       </c>
@@ -5635,7 +5642,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>129</v>
       </c>
@@ -5680,7 +5687,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="62" t="s">
         <v>129</v>
       </c>
@@ -5724,7 +5731,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="62" t="s">
         <v>127</v>
       </c>
@@ -5769,7 +5776,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="62" t="s">
         <v>128</v>
       </c>
@@ -5778,7 +5785,7 @@
         <v>64</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E25" s="106">
         <v>7.1999999999999998E-3</v>
@@ -5814,7 +5821,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="62" t="s">
         <v>127</v>
       </c>
@@ -5859,7 +5866,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="62" t="s">
         <v>129</v>
       </c>
@@ -5904,7 +5911,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="62" t="s">
         <v>129</v>
       </c>
@@ -5949,7 +5956,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="62" t="s">
         <v>129</v>
       </c>
@@ -5994,7 +6001,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="62" t="s">
         <v>127</v>
       </c>
@@ -6039,7 +6046,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="62" t="s">
         <v>128</v>
       </c>
@@ -6084,7 +6091,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="62" t="s">
         <v>127</v>
       </c>
@@ -6129,7 +6136,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="62" t="s">
         <v>129</v>
       </c>
@@ -6174,7 +6181,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="62" t="s">
         <v>129</v>
       </c>
@@ -6219,7 +6226,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="62" t="s">
         <v>129</v>
       </c>
@@ -6264,7 +6271,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="62" t="s">
         <v>127</v>
       </c>
@@ -6309,7 +6316,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="62" t="s">
         <v>128</v>
       </c>
@@ -6354,7 +6361,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="62" t="s">
         <v>127</v>
       </c>
@@ -6399,7 +6406,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>129</v>
       </c>
@@ -6444,10 +6451,10 @@
         <v>0.28000000000000008</v>
       </c>
       <c r="P39" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="62" t="s">
         <v>129</v>
       </c>
@@ -6492,7 +6499,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="62" t="s">
         <v>129</v>
       </c>
@@ -6537,7 +6544,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="62" t="s">
         <v>127</v>
       </c>
@@ -6582,7 +6589,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="62" t="s">
         <v>128</v>
       </c>
@@ -6628,7 +6635,7 @@
       </c>
       <c r="O43" s="44"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="62" t="s">
         <v>127</v>
       </c>
@@ -6674,7 +6681,7 @@
       </c>
       <c r="O44" s="44"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="62" t="s">
         <v>129</v>
       </c>
@@ -6719,7 +6726,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="62" t="s">
         <v>129</v>
       </c>
@@ -6764,7 +6771,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="62" t="s">
         <v>129</v>
       </c>
@@ -6809,7 +6816,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="62" t="s">
         <v>127</v>
       </c>
@@ -6855,7 +6862,7 @@
       </c>
       <c r="P48" s="64"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="62" t="s">
         <v>128</v>
       </c>
@@ -6900,7 +6907,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="62" t="s">
         <v>127</v>
       </c>
@@ -6945,7 +6952,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="62" t="s">
         <v>129</v>
       </c>
@@ -6990,7 +6997,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="62" t="s">
         <v>129</v>
       </c>
@@ -7035,10 +7042,10 @@
         <v>0.4100000000000002</v>
       </c>
       <c r="P52" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="62" t="s">
         <v>129</v>
       </c>
@@ -7083,7 +7090,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="62" t="s">
         <v>127</v>
       </c>
@@ -7128,7 +7135,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="62" t="s">
         <v>128</v>
       </c>
@@ -7173,7 +7180,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="62" t="s">
         <v>127</v>
       </c>
@@ -7218,7 +7225,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="62" t="s">
         <v>129</v>
       </c>
@@ -7263,7 +7270,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="62" t="s">
         <v>129</v>
       </c>
@@ -7308,7 +7315,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="62" t="s">
         <v>129</v>
       </c>
@@ -7353,7 +7360,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="62" t="s">
         <v>127</v>
       </c>
@@ -7398,7 +7405,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="62" t="s">
         <v>128</v>
       </c>
@@ -7443,7 +7450,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="62" t="s">
         <v>127</v>
       </c>
@@ -7488,7 +7495,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="62" t="s">
         <v>129</v>
       </c>
@@ -7533,7 +7540,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="62" t="s">
         <v>129</v>
       </c>
@@ -7578,10 +7585,10 @@
         <v>0.53000000000000025</v>
       </c>
       <c r="P64" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="62" t="s">
         <v>129</v>
       </c>
@@ -7626,7 +7633,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="62" t="s">
         <v>130</v>
       </c>
@@ -7671,7 +7678,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="62" t="s">
         <v>127</v>
       </c>
@@ -7716,7 +7723,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="62" t="s">
         <v>129</v>
       </c>
@@ -7761,7 +7768,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="62" t="s">
         <v>129</v>
       </c>
@@ -7806,7 +7813,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="62" t="s">
         <v>129</v>
       </c>
@@ -7851,7 +7858,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="62" t="s">
         <v>130</v>
       </c>
@@ -7896,7 +7903,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="62" t="s">
         <v>127</v>
       </c>
@@ -7941,7 +7948,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="62" t="s">
         <v>129</v>
       </c>
@@ -7986,7 +7993,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="62" t="s">
         <v>129</v>
       </c>
@@ -8031,7 +8038,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="62" t="s">
         <v>129</v>
       </c>
@@ -8075,7 +8082,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="62" t="s">
         <v>130</v>
       </c>
@@ -8120,7 +8127,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="62" t="s">
         <v>127</v>
       </c>
@@ -8165,7 +8172,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="62" t="s">
         <v>129</v>
       </c>
@@ -8210,7 +8217,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="62" t="s">
         <v>129</v>
       </c>
@@ -8255,7 +8262,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="127" t="s">
         <v>129</v>
       </c>
@@ -8300,7 +8307,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="127"/>
       <c r="B81" s="36"/>
       <c r="C81" s="36" t="s">
@@ -8343,7 +8350,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="127"/>
       <c r="B82" s="36"/>
       <c r="C82" s="36" t="s">
@@ -8386,7 +8393,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="127"/>
       <c r="B83" s="36"/>
       <c r="C83" s="36" t="s">
@@ -8429,7 +8436,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="127"/>
       <c r="B84" s="36"/>
       <c r="C84" s="36" t="s">
@@ -8472,7 +8479,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="127"/>
       <c r="B85" s="36"/>
       <c r="C85" s="36" t="s">
@@ -8515,7 +8522,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="127"/>
       <c r="B86" s="36"/>
       <c r="C86" s="36" t="s">
@@ -8558,7 +8565,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="127"/>
       <c r="B87" s="36"/>
       <c r="C87" s="36" t="s">
@@ -8601,7 +8608,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="127"/>
       <c r="B88" s="36"/>
       <c r="C88" s="36" t="s">
@@ -8644,7 +8651,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="127"/>
       <c r="B89" s="36"/>
       <c r="C89" s="36" t="s">
@@ -8687,7 +8694,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="127"/>
       <c r="B90" s="36"/>
       <c r="C90" s="36" t="s">
@@ -8730,7 +8737,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="127"/>
       <c r="B91" s="36"/>
       <c r="C91" s="36" t="s">
@@ -8773,7 +8780,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="127"/>
       <c r="B92" s="36"/>
       <c r="C92" s="36" t="s">
@@ -8816,7 +8823,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="127"/>
       <c r="B93" s="36"/>
       <c r="C93" s="36" t="s">
@@ -8859,7 +8866,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="127"/>
       <c r="B94" s="36"/>
       <c r="C94" s="36" t="s">
@@ -8902,7 +8909,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="127"/>
       <c r="B95" s="36"/>
       <c r="C95" s="36" t="s">
@@ -8945,7 +8952,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="127"/>
       <c r="B96" s="36"/>
       <c r="C96" s="36" t="s">
@@ -8988,7 +8995,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="127"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36" t="s">
@@ -9031,7 +9038,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="127"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36" t="s">
@@ -9074,7 +9081,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="127"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36" t="s">
@@ -9117,7 +9124,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="127"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36" t="s">
@@ -9160,7 +9167,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="127"/>
       <c r="B101" s="36"/>
       <c r="C101" s="36" t="s">
@@ -9203,7 +9210,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="127"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36" t="s">
@@ -9246,7 +9253,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="127"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36" t="s">
@@ -9289,7 +9296,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="127"/>
       <c r="B104" s="36"/>
       <c r="C104" s="36" t="s">
@@ -9332,7 +9339,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="127"/>
       <c r="B105" s="36"/>
       <c r="C105" s="36" t="s">
@@ -9375,7 +9382,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="127"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36" t="s">
@@ -9418,7 +9425,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="127"/>
       <c r="B107" s="36"/>
       <c r="C107" s="36" t="s">
@@ -9461,7 +9468,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="127"/>
       <c r="B108" s="36"/>
       <c r="C108" s="36" t="s">
@@ -9504,7 +9511,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="127"/>
       <c r="B109" s="36"/>
       <c r="C109" s="36" t="s">
@@ -9547,7 +9554,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="127"/>
       <c r="B110" s="36"/>
       <c r="C110" s="36" t="s">
@@ -9590,7 +9597,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="127"/>
       <c r="B111" s="36"/>
       <c r="C111" s="36" t="s">
@@ -9633,7 +9640,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="154"/>
       <c r="B112" s="36"/>
       <c r="C112" s="36" t="s">
@@ -9676,7 +9683,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="154"/>
       <c r="B113" s="36"/>
       <c r="C113" s="36" t="s">
@@ -9719,7 +9726,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="154"/>
       <c r="B114" s="36"/>
       <c r="C114" s="36" t="s">
@@ -9762,7 +9769,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="154"/>
       <c r="B115" s="36"/>
       <c r="C115" s="36" t="s">
@@ -9805,7 +9812,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="154"/>
       <c r="B116" s="36"/>
       <c r="C116" s="36" t="s">
@@ -9848,7 +9855,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="154"/>
       <c r="B117" s="36"/>
       <c r="C117" s="36" t="s">
@@ -9891,7 +9898,7 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="154"/>
       <c r="B118" s="36"/>
       <c r="C118" s="36" t="s">
@@ -9934,7 +9941,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="154"/>
       <c r="B119" s="36"/>
       <c r="C119" s="36" t="s">
@@ -9977,7 +9984,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="154"/>
       <c r="B120" s="36"/>
       <c r="C120" s="36" t="s">
@@ -10020,7 +10027,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="154"/>
       <c r="B121" s="36"/>
       <c r="C121" s="36" t="s">
@@ -10063,7 +10070,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="154"/>
       <c r="B122" s="36"/>
       <c r="C122" s="36" t="s">
@@ -10106,7 +10113,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="154" t="s">
         <v>29</v>
       </c>
@@ -10154,7 +10161,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="154" t="s">
         <v>29</v>
       </c>
@@ -10202,7 +10209,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="56" t="s">
         <v>29</v>
       </c>
@@ -10219,7 +10226,7 @@
       <c r="L125" s="5"/>
       <c r="M125" s="9"/>
     </row>
-    <row r="126" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="28"/>
       <c r="B126" s="28"/>
       <c r="C126" s="28"/>
@@ -10259,39 +10266,39 @@
       </c>
       <c r="O126" s="64"/>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="J127" s="66">
         <f>J126-K1</f>
-        <v>1447047.6731600082</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C128" s="176"/>
-      <c r="D128" s="176"/>
-      <c r="E128" s="176"/>
-      <c r="F128" s="176"/>
-      <c r="G128" s="176"/>
-      <c r="H128" s="176"/>
-      <c r="I128" s="176"/>
-      <c r="J128" s="176"/>
-      <c r="K128" s="176"/>
-      <c r="L128" s="176"/>
-      <c r="M128" s="176"/>
-    </row>
-    <row r="129" spans="3:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="176"/>
-      <c r="D129" s="176"/>
-      <c r="E129" s="176"/>
-      <c r="F129" s="176"/>
-      <c r="G129" s="176"/>
-      <c r="H129" s="176"/>
-      <c r="I129" s="176"/>
-      <c r="J129" s="176"/>
-      <c r="K129" s="176"/>
-      <c r="L129" s="176"/>
-      <c r="M129" s="176"/>
-    </row>
-    <row r="130" spans="3:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315014.57316000853</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C128" s="172"/>
+      <c r="D128" s="172"/>
+      <c r="E128" s="172"/>
+      <c r="F128" s="172"/>
+      <c r="G128" s="172"/>
+      <c r="H128" s="172"/>
+      <c r="I128" s="172"/>
+      <c r="J128" s="172"/>
+      <c r="K128" s="172"/>
+      <c r="L128" s="172"/>
+      <c r="M128" s="172"/>
+    </row>
+    <row r="129" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C129" s="172"/>
+      <c r="D129" s="172"/>
+      <c r="E129" s="172"/>
+      <c r="F129" s="172"/>
+      <c r="G129" s="172"/>
+      <c r="H129" s="172"/>
+      <c r="I129" s="172"/>
+      <c r="J129" s="172"/>
+      <c r="K129" s="172"/>
+      <c r="L129" s="172"/>
+      <c r="M129" s="172"/>
+    </row>
+    <row r="130" spans="3:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="88"/>
       <c r="D130" s="88"/>
       <c r="E130" s="88"/>
@@ -10304,113 +10311,113 @@
       <c r="L130" s="88"/>
       <c r="M130" s="88"/>
     </row>
-    <row r="131" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C131" s="176" t="s">
-        <v>296</v>
-      </c>
-      <c r="D131" s="176"/>
-      <c r="E131" s="176"/>
-      <c r="F131" s="176"/>
-      <c r="G131" s="176"/>
-      <c r="H131" s="176"/>
-      <c r="I131" s="176"/>
-      <c r="J131" s="176"/>
-      <c r="K131" s="176"/>
-      <c r="L131" s="176"/>
-      <c r="M131" s="176"/>
-    </row>
-    <row r="132" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C132" s="176"/>
-      <c r="D132" s="176"/>
-      <c r="E132" s="176"/>
-      <c r="F132" s="176"/>
-      <c r="G132" s="176"/>
-      <c r="H132" s="176"/>
-      <c r="I132" s="176"/>
-      <c r="J132" s="176"/>
-      <c r="K132" s="176"/>
-      <c r="L132" s="176"/>
-      <c r="M132" s="176"/>
-    </row>
-    <row r="133" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C133" s="176"/>
-      <c r="D133" s="176"/>
-      <c r="E133" s="176"/>
-      <c r="F133" s="176"/>
-      <c r="G133" s="176"/>
-      <c r="H133" s="176"/>
-      <c r="I133" s="176"/>
-      <c r="J133" s="176"/>
-      <c r="K133" s="176"/>
-      <c r="L133" s="176"/>
-      <c r="M133" s="176"/>
-    </row>
-    <row r="134" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C134" s="176"/>
-      <c r="D134" s="176"/>
-      <c r="E134" s="176"/>
-      <c r="F134" s="176"/>
-      <c r="G134" s="176"/>
-      <c r="H134" s="176"/>
-      <c r="I134" s="176"/>
-      <c r="J134" s="176"/>
-      <c r="K134" s="176"/>
-      <c r="L134" s="176"/>
-      <c r="M134" s="176"/>
-    </row>
-    <row r="135" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C135" s="176"/>
-      <c r="D135" s="176"/>
-      <c r="E135" s="176"/>
-      <c r="F135" s="176"/>
-      <c r="G135" s="176"/>
-      <c r="H135" s="176"/>
-      <c r="I135" s="176"/>
-      <c r="J135" s="176"/>
-      <c r="K135" s="176"/>
-      <c r="L135" s="176"/>
-      <c r="M135" s="176"/>
-    </row>
-    <row r="136" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C136" s="176"/>
-      <c r="D136" s="176"/>
-      <c r="E136" s="176"/>
-      <c r="F136" s="176"/>
-      <c r="G136" s="176"/>
-      <c r="H136" s="176"/>
-      <c r="I136" s="176"/>
-      <c r="J136" s="176"/>
-      <c r="K136" s="176"/>
-      <c r="L136" s="176"/>
-      <c r="M136" s="176"/>
-    </row>
-    <row r="137" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C137" s="176"/>
-      <c r="D137" s="176"/>
-      <c r="E137" s="176"/>
-      <c r="F137" s="176"/>
-      <c r="G137" s="176"/>
-      <c r="H137" s="176"/>
-      <c r="I137" s="176"/>
-      <c r="J137" s="176"/>
-      <c r="K137" s="176"/>
-      <c r="L137" s="176"/>
-      <c r="M137" s="176"/>
-    </row>
-    <row r="138" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C138" s="176"/>
-      <c r="D138" s="176"/>
-      <c r="E138" s="176"/>
-      <c r="F138" s="176"/>
-      <c r="G138" s="176"/>
-      <c r="H138" s="176"/>
-      <c r="I138" s="176"/>
-      <c r="J138" s="176"/>
-      <c r="K138" s="176"/>
-      <c r="L138" s="176"/>
-      <c r="M138" s="176"/>
-    </row>
-    <row r="139" spans="3:15" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C131" s="172" t="s">
+        <v>294</v>
+      </c>
+      <c r="D131" s="172"/>
+      <c r="E131" s="172"/>
+      <c r="F131" s="172"/>
+      <c r="G131" s="172"/>
+      <c r="H131" s="172"/>
+      <c r="I131" s="172"/>
+      <c r="J131" s="172"/>
+      <c r="K131" s="172"/>
+      <c r="L131" s="172"/>
+      <c r="M131" s="172"/>
+    </row>
+    <row r="132" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C132" s="172"/>
+      <c r="D132" s="172"/>
+      <c r="E132" s="172"/>
+      <c r="F132" s="172"/>
+      <c r="G132" s="172"/>
+      <c r="H132" s="172"/>
+      <c r="I132" s="172"/>
+      <c r="J132" s="172"/>
+      <c r="K132" s="172"/>
+      <c r="L132" s="172"/>
+      <c r="M132" s="172"/>
+    </row>
+    <row r="133" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C133" s="172"/>
+      <c r="D133" s="172"/>
+      <c r="E133" s="172"/>
+      <c r="F133" s="172"/>
+      <c r="G133" s="172"/>
+      <c r="H133" s="172"/>
+      <c r="I133" s="172"/>
+      <c r="J133" s="172"/>
+      <c r="K133" s="172"/>
+      <c r="L133" s="172"/>
+      <c r="M133" s="172"/>
+    </row>
+    <row r="134" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C134" s="172"/>
+      <c r="D134" s="172"/>
+      <c r="E134" s="172"/>
+      <c r="F134" s="172"/>
+      <c r="G134" s="172"/>
+      <c r="H134" s="172"/>
+      <c r="I134" s="172"/>
+      <c r="J134" s="172"/>
+      <c r="K134" s="172"/>
+      <c r="L134" s="172"/>
+      <c r="M134" s="172"/>
+    </row>
+    <row r="135" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C135" s="172"/>
+      <c r="D135" s="172"/>
+      <c r="E135" s="172"/>
+      <c r="F135" s="172"/>
+      <c r="G135" s="172"/>
+      <c r="H135" s="172"/>
+      <c r="I135" s="172"/>
+      <c r="J135" s="172"/>
+      <c r="K135" s="172"/>
+      <c r="L135" s="172"/>
+      <c r="M135" s="172"/>
+    </row>
+    <row r="136" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C136" s="172"/>
+      <c r="D136" s="172"/>
+      <c r="E136" s="172"/>
+      <c r="F136" s="172"/>
+      <c r="G136" s="172"/>
+      <c r="H136" s="172"/>
+      <c r="I136" s="172"/>
+      <c r="J136" s="172"/>
+      <c r="K136" s="172"/>
+      <c r="L136" s="172"/>
+      <c r="M136" s="172"/>
+    </row>
+    <row r="137" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C137" s="172"/>
+      <c r="D137" s="172"/>
+      <c r="E137" s="172"/>
+      <c r="F137" s="172"/>
+      <c r="G137" s="172"/>
+      <c r="H137" s="172"/>
+      <c r="I137" s="172"/>
+      <c r="J137" s="172"/>
+      <c r="K137" s="172"/>
+      <c r="L137" s="172"/>
+      <c r="M137" s="172"/>
+    </row>
+    <row r="138" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C138" s="172"/>
+      <c r="D138" s="172"/>
+      <c r="E138" s="172"/>
+      <c r="F138" s="172"/>
+      <c r="G138" s="172"/>
+      <c r="H138" s="172"/>
+      <c r="I138" s="172"/>
+      <c r="J138" s="172"/>
+      <c r="K138" s="172"/>
+      <c r="L138" s="172"/>
+      <c r="M138" s="172"/>
+    </row>
+    <row r="139" spans="3:15" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="88"/>
       <c r="D139" s="88"/>
       <c r="E139" s="88"/>
@@ -10423,7 +10430,7 @@
       <c r="L139" s="88"/>
       <c r="M139" s="88"/>
     </row>
-    <row r="140" spans="3:15" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:15" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="88"/>
       <c r="D140" s="88"/>
       <c r="E140" s="88"/>
@@ -10436,105 +10443,110 @@
       <c r="L140" s="88"/>
       <c r="M140" s="88"/>
     </row>
-    <row r="141" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C141" s="175" t="s">
-        <v>295</v>
-      </c>
-      <c r="D141" s="175"/>
-      <c r="E141" s="175"/>
-      <c r="F141" s="175"/>
-      <c r="G141" s="175"/>
-      <c r="H141" s="175"/>
-      <c r="I141" s="175"/>
-      <c r="J141" s="175"/>
-      <c r="K141" s="175"/>
-      <c r="L141" s="175"/>
-      <c r="M141" s="175"/>
-    </row>
-    <row r="142" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C142" s="175"/>
-      <c r="D142" s="175"/>
-      <c r="E142" s="175"/>
-      <c r="F142" s="175"/>
-      <c r="G142" s="175"/>
-      <c r="H142" s="175"/>
-      <c r="I142" s="175"/>
-      <c r="J142" s="175"/>
-      <c r="K142" s="175"/>
-      <c r="L142" s="175"/>
-      <c r="M142" s="175"/>
-    </row>
-    <row r="143" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C143" s="175"/>
-      <c r="D143" s="175"/>
-      <c r="E143" s="175"/>
-      <c r="F143" s="175"/>
-      <c r="G143" s="175"/>
-      <c r="H143" s="175"/>
-      <c r="I143" s="175"/>
-      <c r="J143" s="175"/>
-      <c r="K143" s="175"/>
-      <c r="L143" s="175"/>
-      <c r="M143" s="175"/>
+    <row r="141" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C141" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="D141" s="171"/>
+      <c r="E141" s="171"/>
+      <c r="F141" s="171"/>
+      <c r="G141" s="171"/>
+      <c r="H141" s="171"/>
+      <c r="I141" s="171"/>
+      <c r="J141" s="171"/>
+      <c r="K141" s="171"/>
+      <c r="L141" s="171"/>
+      <c r="M141" s="171"/>
+    </row>
+    <row r="142" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C142" s="171"/>
+      <c r="D142" s="171"/>
+      <c r="E142" s="171"/>
+      <c r="F142" s="171"/>
+      <c r="G142" s="171"/>
+      <c r="H142" s="171"/>
+      <c r="I142" s="171"/>
+      <c r="J142" s="171"/>
+      <c r="K142" s="171"/>
+      <c r="L142" s="171"/>
+      <c r="M142" s="171"/>
+    </row>
+    <row r="143" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C143" s="171"/>
+      <c r="D143" s="171"/>
+      <c r="E143" s="171"/>
+      <c r="F143" s="171"/>
+      <c r="G143" s="171"/>
+      <c r="H143" s="171"/>
+      <c r="I143" s="171"/>
+      <c r="J143" s="171"/>
+      <c r="K143" s="171"/>
+      <c r="L143" s="171"/>
+      <c r="M143" s="171"/>
       <c r="O143" s="96">
         <f>K1-J126</f>
-        <v>-1447047.6731600082</v>
-      </c>
-    </row>
-    <row r="144" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C144" s="175"/>
-      <c r="D144" s="175"/>
-      <c r="E144" s="175"/>
-      <c r="F144" s="175"/>
-      <c r="G144" s="175"/>
-      <c r="H144" s="175"/>
-      <c r="I144" s="175"/>
-      <c r="J144" s="175"/>
-      <c r="K144" s="175"/>
-      <c r="L144" s="175"/>
-      <c r="M144" s="175"/>
-    </row>
-    <row r="145" spans="3:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="175"/>
-      <c r="D145" s="175"/>
-      <c r="E145" s="175"/>
-      <c r="F145" s="175"/>
-      <c r="G145" s="175"/>
-      <c r="H145" s="175"/>
-      <c r="I145" s="175"/>
-      <c r="J145" s="175"/>
-      <c r="K145" s="175"/>
-      <c r="L145" s="175"/>
-      <c r="M145" s="175"/>
-    </row>
-    <row r="146" spans="3:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="175"/>
-      <c r="D146" s="175"/>
-      <c r="E146" s="175"/>
-      <c r="F146" s="175"/>
-      <c r="G146" s="175"/>
-      <c r="H146" s="175"/>
-      <c r="I146" s="175"/>
-      <c r="J146" s="175"/>
-      <c r="K146" s="175"/>
-      <c r="L146" s="175"/>
-      <c r="M146" s="175"/>
-    </row>
-    <row r="147" spans="3:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="175"/>
-      <c r="D147" s="175"/>
-      <c r="E147" s="175"/>
-      <c r="F147" s="175"/>
-      <c r="G147" s="175"/>
-      <c r="H147" s="175"/>
-      <c r="I147" s="175"/>
-      <c r="J147" s="175"/>
-      <c r="K147" s="175"/>
-      <c r="L147" s="175"/>
-      <c r="M147" s="175"/>
+        <v>-315014.57316000853</v>
+      </c>
+    </row>
+    <row r="144" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C144" s="171"/>
+      <c r="D144" s="171"/>
+      <c r="E144" s="171"/>
+      <c r="F144" s="171"/>
+      <c r="G144" s="171"/>
+      <c r="H144" s="171"/>
+      <c r="I144" s="171"/>
+      <c r="J144" s="171"/>
+      <c r="K144" s="171"/>
+      <c r="L144" s="171"/>
+      <c r="M144" s="171"/>
+    </row>
+    <row r="145" spans="3:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="171"/>
+      <c r="D145" s="171"/>
+      <c r="E145" s="171"/>
+      <c r="F145" s="171"/>
+      <c r="G145" s="171"/>
+      <c r="H145" s="171"/>
+      <c r="I145" s="171"/>
+      <c r="J145" s="171"/>
+      <c r="K145" s="171"/>
+      <c r="L145" s="171"/>
+      <c r="M145" s="171"/>
+    </row>
+    <row r="146" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="171"/>
+      <c r="D146" s="171"/>
+      <c r="E146" s="171"/>
+      <c r="F146" s="171"/>
+      <c r="G146" s="171"/>
+      <c r="H146" s="171"/>
+      <c r="I146" s="171"/>
+      <c r="J146" s="171"/>
+      <c r="K146" s="171"/>
+      <c r="L146" s="171"/>
+      <c r="M146" s="171"/>
+    </row>
+    <row r="147" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="171"/>
+      <c r="D147" s="171"/>
+      <c r="E147" s="171"/>
+      <c r="F147" s="171"/>
+      <c r="G147" s="171"/>
+      <c r="H147" s="171"/>
+      <c r="I147" s="171"/>
+      <c r="J147" s="171"/>
+      <c r="K147" s="171"/>
+      <c r="L147" s="171"/>
+      <c r="M147" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P7:Q8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C141:M147"/>
@@ -10548,15 +10560,25 @@
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="C131:M138"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
+  <dimension ref="B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/EL MIRADOR/Junio/JUNIO - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Junio/JUNIO - EL MIRADOR .xlsx
@@ -1,32 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FDB61A-1F73-4E73-9859-E755BF35361C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36667721-C541-4F53-8111-9E5D67628533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
+    <sheet name="SUELDOS" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$148</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">SUELDOS!$A$2:$J$27</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="307">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -939,6 +941,15 @@
   </si>
   <si>
     <t>AGREGAR MAILS DEL FOLEO</t>
+  </si>
+  <si>
+    <t>Firma</t>
+  </si>
+  <si>
+    <t>__________________________________</t>
+  </si>
+  <si>
+    <t>Aclaracion</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1515,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1703,6 +1714,9 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1733,14 +1747,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1775,21 +1801,30 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2335,66 +2370,66 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="158" t="s">
+      <c r="A14" s="161" t="s">
         <v>294</v>
       </c>
-      <c r="B14" s="158"/>
-      <c r="C14" s="158"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="158"/>
-      <c r="F14" s="158"/>
-      <c r="G14" s="158"/>
-      <c r="H14" s="158"/>
-      <c r="I14" s="158"/>
-      <c r="J14" s="158"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="161"/>
+      <c r="G14" s="161"/>
+      <c r="H14" s="161"/>
+      <c r="I14" s="161"/>
+      <c r="J14" s="161"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="158"/>
-      <c r="I15" s="158"/>
-      <c r="J15" s="158"/>
+      <c r="A15" s="161"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="161"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="158"/>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-      <c r="J16" s="158"/>
+      <c r="A16" s="161"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="161"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="158"/>
-      <c r="G17" s="158"/>
-      <c r="H17" s="158"/>
-      <c r="I17" s="158"/>
-      <c r="J17" s="158"/>
+      <c r="A17" s="161"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="161"/>
+      <c r="D17" s="161"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="161"/>
+      <c r="J17" s="161"/>
     </row>
     <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="158"/>
-      <c r="B18" s="158"/>
-      <c r="C18" s="158"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="158"/>
-      <c r="I18" s="158"/>
-      <c r="J18" s="158"/>
+      <c r="A18" s="161"/>
+      <c r="B18" s="161"/>
+      <c r="C18" s="161"/>
+      <c r="D18" s="161"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="161"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="161"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
@@ -2964,7 +2999,7 @@
       <c r="C50" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="D50" s="187">
+      <c r="D50" s="159">
         <v>643422</v>
       </c>
       <c r="E50" s="50"/>
@@ -3129,7 +3164,7 @@
       <c r="C57" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D57" s="188">
+      <c r="D57" s="160">
         <v>160913</v>
       </c>
       <c r="E57" s="63">
@@ -3170,7 +3205,7 @@
       <c r="C58" s="36" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="188">
+      <c r="D58" s="160">
         <v>7907</v>
       </c>
       <c r="E58" s="63">
@@ -3211,7 +3246,7 @@
       <c r="C59" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="D59" s="188">
+      <c r="D59" s="160">
         <v>7907</v>
       </c>
       <c r="E59" s="63">
@@ -3362,7 +3397,7 @@
       <c r="C63" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D63" s="186">
+      <c r="D63" s="158">
         <v>1233986.03</v>
       </c>
       <c r="E63" s="74">
@@ -4424,12 +4459,12 @@
       <c r="I103" s="65"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="164" t="s">
+      <c r="A104" s="167" t="s">
         <v>39</v>
       </c>
-      <c r="B104" s="165"/>
-      <c r="C104" s="165"/>
-      <c r="D104" s="165"/>
+      <c r="B104" s="168"/>
+      <c r="C104" s="168"/>
+      <c r="D104" s="168"/>
       <c r="E104" s="91" t="s">
         <v>12</v>
       </c>
@@ -4450,8 +4485,8 @@
       </c>
     </row>
     <row r="105" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="166"/>
-      <c r="B105" s="167"/>
+      <c r="A105" s="169"/>
+      <c r="B105" s="170"/>
       <c r="C105" s="93"/>
       <c r="D105" s="45"/>
       <c r="E105" s="74">
@@ -4465,8 +4500,8 @@
       <c r="J105" s="63"/>
     </row>
     <row r="106" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="166"/>
-      <c r="B106" s="167"/>
+      <c r="A106" s="169"/>
+      <c r="B106" s="170"/>
       <c r="C106" s="93"/>
       <c r="D106" s="45"/>
       <c r="E106" s="74"/>
@@ -4477,11 +4512,11 @@
       <c r="J106" s="63"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="161" t="s">
+      <c r="A107" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="B107" s="162"/>
-      <c r="C107" s="163"/>
+      <c r="B107" s="165"/>
+      <c r="C107" s="166"/>
       <c r="D107" s="90">
         <f>SUM(D105:D106)</f>
         <v>0</v>
@@ -4533,8 +4568,8 @@
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D112" s="160"/>
-      <c r="E112" s="160"/>
+      <c r="D112" s="163"/>
+      <c r="E112" s="163"/>
       <c r="F112" s="104"/>
       <c r="G112" s="104"/>
       <c r="H112" s="104"/>
@@ -4546,8 +4581,8 @@
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="19"/>
-      <c r="D113" s="160"/>
-      <c r="E113" s="160"/>
+      <c r="D113" s="163"/>
+      <c r="E113" s="163"/>
       <c r="F113" s="104"/>
       <c r="G113" s="104"/>
       <c r="H113" s="104"/>
@@ -4561,8 +4596,8 @@
         <v>7250000</v>
       </c>
       <c r="C114" s="21"/>
-      <c r="D114" s="160"/>
-      <c r="E114" s="160"/>
+      <c r="D114" s="163"/>
+      <c r="E114" s="163"/>
       <c r="F114" s="104"/>
       <c r="G114" s="104"/>
       <c r="H114" s="104"/>
@@ -4579,8 +4614,8 @@
       <c r="C115" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D115" s="160"/>
-      <c r="E115" s="160"/>
+      <c r="D115" s="163"/>
+      <c r="E115" s="163"/>
       <c r="F115" s="104"/>
       <c r="G115" s="104"/>
       <c r="H115" s="104"/>
@@ -4595,8 +4630,8 @@
         <v>-6774628.959999999</v>
       </c>
       <c r="C116" s="19"/>
-      <c r="D116" s="160"/>
-      <c r="E116" s="160"/>
+      <c r="D116" s="163"/>
+      <c r="E116" s="163"/>
       <c r="F116" s="104"/>
       <c r="G116" s="104"/>
       <c r="H116" s="104"/>
@@ -4612,8 +4647,8 @@
         <v>0</v>
       </c>
       <c r="C117" s="19"/>
-      <c r="D117" s="160"/>
-      <c r="E117" s="160"/>
+      <c r="D117" s="163"/>
+      <c r="E117" s="163"/>
       <c r="F117" s="104"/>
       <c r="G117" s="104"/>
       <c r="H117" s="104"/>
@@ -4730,50 +4765,50 @@
       <c r="R131" s="10"/>
     </row>
     <row r="134" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B134" s="159"/>
-      <c r="C134" s="159"/>
-      <c r="D134" s="159"/>
-      <c r="E134" s="159"/>
+      <c r="B134" s="162"/>
+      <c r="C134" s="162"/>
+      <c r="D134" s="162"/>
+      <c r="E134" s="162"/>
       <c r="F134" s="108"/>
       <c r="G134" s="108"/>
       <c r="H134" s="108"/>
       <c r="I134" s="108"/>
     </row>
     <row r="135" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B135" s="159"/>
-      <c r="C135" s="159"/>
-      <c r="D135" s="159"/>
-      <c r="E135" s="159"/>
+      <c r="B135" s="162"/>
+      <c r="C135" s="162"/>
+      <c r="D135" s="162"/>
+      <c r="E135" s="162"/>
       <c r="F135" s="108"/>
       <c r="G135" s="108"/>
       <c r="H135" s="108"/>
       <c r="I135" s="108"/>
     </row>
     <row r="136" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B136" s="159"/>
-      <c r="C136" s="159"/>
-      <c r="D136" s="159"/>
-      <c r="E136" s="159"/>
+      <c r="B136" s="162"/>
+      <c r="C136" s="162"/>
+      <c r="D136" s="162"/>
+      <c r="E136" s="162"/>
       <c r="F136" s="108"/>
       <c r="G136" s="108"/>
       <c r="H136" s="108"/>
       <c r="I136" s="108"/>
     </row>
     <row r="137" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B137" s="159"/>
-      <c r="C137" s="159"/>
-      <c r="D137" s="159"/>
-      <c r="E137" s="159"/>
+      <c r="B137" s="162"/>
+      <c r="C137" s="162"/>
+      <c r="D137" s="162"/>
+      <c r="E137" s="162"/>
       <c r="F137" s="108"/>
       <c r="G137" s="108"/>
       <c r="H137" s="108"/>
       <c r="I137" s="108"/>
     </row>
     <row r="138" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B138" s="159"/>
-      <c r="C138" s="159"/>
-      <c r="D138" s="159"/>
-      <c r="E138" s="159"/>
+      <c r="B138" s="162"/>
+      <c r="C138" s="162"/>
+      <c r="D138" s="162"/>
+      <c r="E138" s="162"/>
       <c r="F138" s="108"/>
       <c r="G138" s="108"/>
       <c r="H138" s="108"/>
@@ -4831,11 +4866,11 @@
       <c r="J1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="173">
+      <c r="K1" s="180">
         <f>RESUMEN!D96-RESUMEN!D94</f>
         <v>6774628.959999999</v>
       </c>
-      <c r="L1" s="174"/>
+      <c r="L1" s="181"/>
       <c r="M1" s="77"/>
       <c r="N1" s="64"/>
     </row>
@@ -4901,60 +4936,60 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="169" t="s">
+      <c r="C5" s="171" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="184" t="s">
+      <c r="D5" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="171" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="169" t="s">
+      <c r="F5" s="171" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="171" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="177" t="s">
+      <c r="H5" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="175" t="s">
+      <c r="I5" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="175" t="s">
+      <c r="J5" s="182" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="180" t="s">
+      <c r="K5" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="175" t="s">
+      <c r="L5" s="182" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="175" t="s">
+      <c r="M5" s="182" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="170"/>
-      <c r="B6" s="183"/>
-      <c r="C6" s="170"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="170"/>
-      <c r="G6" s="170"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="179"/>
-      <c r="K6" s="181"/>
-      <c r="L6" s="179"/>
-      <c r="M6" s="176"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="186"/>
+      <c r="K6" s="188"/>
+      <c r="L6" s="186"/>
+      <c r="M6" s="183"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -4994,10 +5029,10 @@
         <v>75258.711480960017</v>
       </c>
       <c r="N7" s="138"/>
-      <c r="P7" s="168" t="s">
+      <c r="P7" s="177" t="s">
         <v>288</v>
       </c>
-      <c r="Q7" s="168"/>
+      <c r="Q7" s="177"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -5036,8 +5071,8 @@
         <v>89195.509903359998</v>
       </c>
       <c r="N8" s="138"/>
-      <c r="P8" s="168"/>
-      <c r="Q8" s="168"/>
+      <c r="P8" s="177"/>
+      <c r="Q8" s="177"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -10273,30 +10308,30 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C128" s="172"/>
-      <c r="D128" s="172"/>
-      <c r="E128" s="172"/>
-      <c r="F128" s="172"/>
-      <c r="G128" s="172"/>
-      <c r="H128" s="172"/>
-      <c r="I128" s="172"/>
-      <c r="J128" s="172"/>
-      <c r="K128" s="172"/>
-      <c r="L128" s="172"/>
-      <c r="M128" s="172"/>
+      <c r="C128" s="179"/>
+      <c r="D128" s="179"/>
+      <c r="E128" s="179"/>
+      <c r="F128" s="179"/>
+      <c r="G128" s="179"/>
+      <c r="H128" s="179"/>
+      <c r="I128" s="179"/>
+      <c r="J128" s="179"/>
+      <c r="K128" s="179"/>
+      <c r="L128" s="179"/>
+      <c r="M128" s="179"/>
     </row>
     <row r="129" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C129" s="172"/>
-      <c r="D129" s="172"/>
-      <c r="E129" s="172"/>
-      <c r="F129" s="172"/>
-      <c r="G129" s="172"/>
-      <c r="H129" s="172"/>
-      <c r="I129" s="172"/>
-      <c r="J129" s="172"/>
-      <c r="K129" s="172"/>
-      <c r="L129" s="172"/>
-      <c r="M129" s="172"/>
+      <c r="C129" s="179"/>
+      <c r="D129" s="179"/>
+      <c r="E129" s="179"/>
+      <c r="F129" s="179"/>
+      <c r="G129" s="179"/>
+      <c r="H129" s="179"/>
+      <c r="I129" s="179"/>
+      <c r="J129" s="179"/>
+      <c r="K129" s="179"/>
+      <c r="L129" s="179"/>
+      <c r="M129" s="179"/>
     </row>
     <row r="130" spans="3:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="88"/>
@@ -10312,110 +10347,110 @@
       <c r="M130" s="88"/>
     </row>
     <row r="131" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C131" s="172" t="s">
+      <c r="C131" s="179" t="s">
         <v>294</v>
       </c>
-      <c r="D131" s="172"/>
-      <c r="E131" s="172"/>
-      <c r="F131" s="172"/>
-      <c r="G131" s="172"/>
-      <c r="H131" s="172"/>
-      <c r="I131" s="172"/>
-      <c r="J131" s="172"/>
-      <c r="K131" s="172"/>
-      <c r="L131" s="172"/>
-      <c r="M131" s="172"/>
+      <c r="D131" s="179"/>
+      <c r="E131" s="179"/>
+      <c r="F131" s="179"/>
+      <c r="G131" s="179"/>
+      <c r="H131" s="179"/>
+      <c r="I131" s="179"/>
+      <c r="J131" s="179"/>
+      <c r="K131" s="179"/>
+      <c r="L131" s="179"/>
+      <c r="M131" s="179"/>
     </row>
     <row r="132" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C132" s="172"/>
-      <c r="D132" s="172"/>
-      <c r="E132" s="172"/>
-      <c r="F132" s="172"/>
-      <c r="G132" s="172"/>
-      <c r="H132" s="172"/>
-      <c r="I132" s="172"/>
-      <c r="J132" s="172"/>
-      <c r="K132" s="172"/>
-      <c r="L132" s="172"/>
-      <c r="M132" s="172"/>
+      <c r="C132" s="179"/>
+      <c r="D132" s="179"/>
+      <c r="E132" s="179"/>
+      <c r="F132" s="179"/>
+      <c r="G132" s="179"/>
+      <c r="H132" s="179"/>
+      <c r="I132" s="179"/>
+      <c r="J132" s="179"/>
+      <c r="K132" s="179"/>
+      <c r="L132" s="179"/>
+      <c r="M132" s="179"/>
     </row>
     <row r="133" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C133" s="172"/>
-      <c r="D133" s="172"/>
-      <c r="E133" s="172"/>
-      <c r="F133" s="172"/>
-      <c r="G133" s="172"/>
-      <c r="H133" s="172"/>
-      <c r="I133" s="172"/>
-      <c r="J133" s="172"/>
-      <c r="K133" s="172"/>
-      <c r="L133" s="172"/>
-      <c r="M133" s="172"/>
+      <c r="C133" s="179"/>
+      <c r="D133" s="179"/>
+      <c r="E133" s="179"/>
+      <c r="F133" s="179"/>
+      <c r="G133" s="179"/>
+      <c r="H133" s="179"/>
+      <c r="I133" s="179"/>
+      <c r="J133" s="179"/>
+      <c r="K133" s="179"/>
+      <c r="L133" s="179"/>
+      <c r="M133" s="179"/>
     </row>
     <row r="134" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C134" s="172"/>
-      <c r="D134" s="172"/>
-      <c r="E134" s="172"/>
-      <c r="F134" s="172"/>
-      <c r="G134" s="172"/>
-      <c r="H134" s="172"/>
-      <c r="I134" s="172"/>
-      <c r="J134" s="172"/>
-      <c r="K134" s="172"/>
-      <c r="L134" s="172"/>
-      <c r="M134" s="172"/>
+      <c r="C134" s="179"/>
+      <c r="D134" s="179"/>
+      <c r="E134" s="179"/>
+      <c r="F134" s="179"/>
+      <c r="G134" s="179"/>
+      <c r="H134" s="179"/>
+      <c r="I134" s="179"/>
+      <c r="J134" s="179"/>
+      <c r="K134" s="179"/>
+      <c r="L134" s="179"/>
+      <c r="M134" s="179"/>
     </row>
     <row r="135" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C135" s="172"/>
-      <c r="D135" s="172"/>
-      <c r="E135" s="172"/>
-      <c r="F135" s="172"/>
-      <c r="G135" s="172"/>
-      <c r="H135" s="172"/>
-      <c r="I135" s="172"/>
-      <c r="J135" s="172"/>
-      <c r="K135" s="172"/>
-      <c r="L135" s="172"/>
-      <c r="M135" s="172"/>
+      <c r="C135" s="179"/>
+      <c r="D135" s="179"/>
+      <c r="E135" s="179"/>
+      <c r="F135" s="179"/>
+      <c r="G135" s="179"/>
+      <c r="H135" s="179"/>
+      <c r="I135" s="179"/>
+      <c r="J135" s="179"/>
+      <c r="K135" s="179"/>
+      <c r="L135" s="179"/>
+      <c r="M135" s="179"/>
     </row>
     <row r="136" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C136" s="172"/>
-      <c r="D136" s="172"/>
-      <c r="E136" s="172"/>
-      <c r="F136" s="172"/>
-      <c r="G136" s="172"/>
-      <c r="H136" s="172"/>
-      <c r="I136" s="172"/>
-      <c r="J136" s="172"/>
-      <c r="K136" s="172"/>
-      <c r="L136" s="172"/>
-      <c r="M136" s="172"/>
+      <c r="C136" s="179"/>
+      <c r="D136" s="179"/>
+      <c r="E136" s="179"/>
+      <c r="F136" s="179"/>
+      <c r="G136" s="179"/>
+      <c r="H136" s="179"/>
+      <c r="I136" s="179"/>
+      <c r="J136" s="179"/>
+      <c r="K136" s="179"/>
+      <c r="L136" s="179"/>
+      <c r="M136" s="179"/>
     </row>
     <row r="137" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C137" s="172"/>
-      <c r="D137" s="172"/>
-      <c r="E137" s="172"/>
-      <c r="F137" s="172"/>
-      <c r="G137" s="172"/>
-      <c r="H137" s="172"/>
-      <c r="I137" s="172"/>
-      <c r="J137" s="172"/>
-      <c r="K137" s="172"/>
-      <c r="L137" s="172"/>
-      <c r="M137" s="172"/>
+      <c r="C137" s="179"/>
+      <c r="D137" s="179"/>
+      <c r="E137" s="179"/>
+      <c r="F137" s="179"/>
+      <c r="G137" s="179"/>
+      <c r="H137" s="179"/>
+      <c r="I137" s="179"/>
+      <c r="J137" s="179"/>
+      <c r="K137" s="179"/>
+      <c r="L137" s="179"/>
+      <c r="M137" s="179"/>
     </row>
     <row r="138" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C138" s="172"/>
-      <c r="D138" s="172"/>
-      <c r="E138" s="172"/>
-      <c r="F138" s="172"/>
-      <c r="G138" s="172"/>
-      <c r="H138" s="172"/>
-      <c r="I138" s="172"/>
-      <c r="J138" s="172"/>
-      <c r="K138" s="172"/>
-      <c r="L138" s="172"/>
-      <c r="M138" s="172"/>
+      <c r="C138" s="179"/>
+      <c r="D138" s="179"/>
+      <c r="E138" s="179"/>
+      <c r="F138" s="179"/>
+      <c r="G138" s="179"/>
+      <c r="H138" s="179"/>
+      <c r="I138" s="179"/>
+      <c r="J138" s="179"/>
+      <c r="K138" s="179"/>
+      <c r="L138" s="179"/>
+      <c r="M138" s="179"/>
     </row>
     <row r="139" spans="3:15" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="88"/>
@@ -10444,109 +10479,104 @@
       <c r="M140" s="88"/>
     </row>
     <row r="141" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C141" s="171" t="s">
+      <c r="C141" s="178" t="s">
         <v>293</v>
       </c>
-      <c r="D141" s="171"/>
-      <c r="E141" s="171"/>
-      <c r="F141" s="171"/>
-      <c r="G141" s="171"/>
-      <c r="H141" s="171"/>
-      <c r="I141" s="171"/>
-      <c r="J141" s="171"/>
-      <c r="K141" s="171"/>
-      <c r="L141" s="171"/>
-      <c r="M141" s="171"/>
+      <c r="D141" s="178"/>
+      <c r="E141" s="178"/>
+      <c r="F141" s="178"/>
+      <c r="G141" s="178"/>
+      <c r="H141" s="178"/>
+      <c r="I141" s="178"/>
+      <c r="J141" s="178"/>
+      <c r="K141" s="178"/>
+      <c r="L141" s="178"/>
+      <c r="M141" s="178"/>
     </row>
     <row r="142" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C142" s="171"/>
-      <c r="D142" s="171"/>
-      <c r="E142" s="171"/>
-      <c r="F142" s="171"/>
-      <c r="G142" s="171"/>
-      <c r="H142" s="171"/>
-      <c r="I142" s="171"/>
-      <c r="J142" s="171"/>
-      <c r="K142" s="171"/>
-      <c r="L142" s="171"/>
-      <c r="M142" s="171"/>
+      <c r="C142" s="178"/>
+      <c r="D142" s="178"/>
+      <c r="E142" s="178"/>
+      <c r="F142" s="178"/>
+      <c r="G142" s="178"/>
+      <c r="H142" s="178"/>
+      <c r="I142" s="178"/>
+      <c r="J142" s="178"/>
+      <c r="K142" s="178"/>
+      <c r="L142" s="178"/>
+      <c r="M142" s="178"/>
     </row>
     <row r="143" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C143" s="171"/>
-      <c r="D143" s="171"/>
-      <c r="E143" s="171"/>
-      <c r="F143" s="171"/>
-      <c r="G143" s="171"/>
-      <c r="H143" s="171"/>
-      <c r="I143" s="171"/>
-      <c r="J143" s="171"/>
-      <c r="K143" s="171"/>
-      <c r="L143" s="171"/>
-      <c r="M143" s="171"/>
+      <c r="C143" s="178"/>
+      <c r="D143" s="178"/>
+      <c r="E143" s="178"/>
+      <c r="F143" s="178"/>
+      <c r="G143" s="178"/>
+      <c r="H143" s="178"/>
+      <c r="I143" s="178"/>
+      <c r="J143" s="178"/>
+      <c r="K143" s="178"/>
+      <c r="L143" s="178"/>
+      <c r="M143" s="178"/>
       <c r="O143" s="96">
         <f>K1-J126</f>
         <v>-315014.57316000853</v>
       </c>
     </row>
     <row r="144" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C144" s="171"/>
-      <c r="D144" s="171"/>
-      <c r="E144" s="171"/>
-      <c r="F144" s="171"/>
-      <c r="G144" s="171"/>
-      <c r="H144" s="171"/>
-      <c r="I144" s="171"/>
-      <c r="J144" s="171"/>
-      <c r="K144" s="171"/>
-      <c r="L144" s="171"/>
-      <c r="M144" s="171"/>
+      <c r="C144" s="178"/>
+      <c r="D144" s="178"/>
+      <c r="E144" s="178"/>
+      <c r="F144" s="178"/>
+      <c r="G144" s="178"/>
+      <c r="H144" s="178"/>
+      <c r="I144" s="178"/>
+      <c r="J144" s="178"/>
+      <c r="K144" s="178"/>
+      <c r="L144" s="178"/>
+      <c r="M144" s="178"/>
     </row>
     <row r="145" spans="3:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C145" s="171"/>
-      <c r="D145" s="171"/>
-      <c r="E145" s="171"/>
-      <c r="F145" s="171"/>
-      <c r="G145" s="171"/>
-      <c r="H145" s="171"/>
-      <c r="I145" s="171"/>
-      <c r="J145" s="171"/>
-      <c r="K145" s="171"/>
-      <c r="L145" s="171"/>
-      <c r="M145" s="171"/>
+      <c r="C145" s="178"/>
+      <c r="D145" s="178"/>
+      <c r="E145" s="178"/>
+      <c r="F145" s="178"/>
+      <c r="G145" s="178"/>
+      <c r="H145" s="178"/>
+      <c r="I145" s="178"/>
+      <c r="J145" s="178"/>
+      <c r="K145" s="178"/>
+      <c r="L145" s="178"/>
+      <c r="M145" s="178"/>
     </row>
     <row r="146" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C146" s="171"/>
-      <c r="D146" s="171"/>
-      <c r="E146" s="171"/>
-      <c r="F146" s="171"/>
-      <c r="G146" s="171"/>
-      <c r="H146" s="171"/>
-      <c r="I146" s="171"/>
-      <c r="J146" s="171"/>
-      <c r="K146" s="171"/>
-      <c r="L146" s="171"/>
-      <c r="M146" s="171"/>
+      <c r="C146" s="178"/>
+      <c r="D146" s="178"/>
+      <c r="E146" s="178"/>
+      <c r="F146" s="178"/>
+      <c r="G146" s="178"/>
+      <c r="H146" s="178"/>
+      <c r="I146" s="178"/>
+      <c r="J146" s="178"/>
+      <c r="K146" s="178"/>
+      <c r="L146" s="178"/>
+      <c r="M146" s="178"/>
     </row>
     <row r="147" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="171"/>
-      <c r="D147" s="171"/>
-      <c r="E147" s="171"/>
-      <c r="F147" s="171"/>
-      <c r="G147" s="171"/>
-      <c r="H147" s="171"/>
-      <c r="I147" s="171"/>
-      <c r="J147" s="171"/>
-      <c r="K147" s="171"/>
-      <c r="L147" s="171"/>
-      <c r="M147" s="171"/>
+      <c r="C147" s="178"/>
+      <c r="D147" s="178"/>
+      <c r="E147" s="178"/>
+      <c r="F147" s="178"/>
+      <c r="G147" s="178"/>
+      <c r="H147" s="178"/>
+      <c r="I147" s="178"/>
+      <c r="J147" s="178"/>
+      <c r="K147" s="178"/>
+      <c r="L147" s="178"/>
+      <c r="M147" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P7:Q8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C141:M147"/>
@@ -10560,6 +10590,11 @@
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="C131:M138"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10581,4 +10616,362 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F259CFE1-42D2-4AD8-B863-5EC1A49F4085}">
+  <dimension ref="A2:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="194" t="str">
+        <f>RESUMEN!C5</f>
+        <v>PERÍODO: JULIO</v>
+      </c>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195" t="str">
+        <f>RESUMEN!A22</f>
+        <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+      </c>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="196"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="190"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="str">
+        <f>RESUMEN!A23</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="197">
+        <f>RESUMEN!D23</f>
+        <v>963000</v>
+      </c>
+      <c r="H5" s="201" t="s">
+        <v>304</v>
+      </c>
+      <c r="I5" s="201"/>
+      <c r="J5" s="202"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="str">
+        <f>RESUMEN!A24</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="197">
+        <f>RESUMEN!D24</f>
+        <v>33606.9</v>
+      </c>
+      <c r="H6" s="201" t="s">
+        <v>305</v>
+      </c>
+      <c r="I6" s="201"/>
+      <c r="J6" s="202"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="str">
+        <f>RESUMEN!A25</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="197">
+        <f>RESUMEN!D25</f>
+        <v>111256.4</v>
+      </c>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="202"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="str">
+        <f>RESUMEN!A26</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="D8" s="189"/>
+      <c r="E8" s="189"/>
+      <c r="F8" s="189"/>
+      <c r="G8" s="197">
+        <f>RESUMEN!D26</f>
+        <v>19877.400000000001</v>
+      </c>
+      <c r="H8" s="189"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="190"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="str">
+        <f>RESUMEN!A27</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="D9" s="189"/>
+      <c r="E9" s="189"/>
+      <c r="F9" s="189"/>
+      <c r="G9" s="197">
+        <f>RESUMEN!D27</f>
+        <v>50000</v>
+      </c>
+      <c r="H9" s="201" t="s">
+        <v>306</v>
+      </c>
+      <c r="I9" s="201"/>
+      <c r="J9" s="202"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="str">
+        <f>RESUMEN!A28</f>
+        <v>SAC</v>
+      </c>
+      <c r="D10" s="189"/>
+      <c r="E10" s="189"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="197">
+        <f>RESUMEN!D28</f>
+        <v>410000</v>
+      </c>
+      <c r="H10" s="201" t="s">
+        <v>305</v>
+      </c>
+      <c r="I10" s="201"/>
+      <c r="J10" s="202"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+      <c r="D11" s="189"/>
+      <c r="E11" s="189"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="189"/>
+      <c r="H11" s="201"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="202"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="198" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="200">
+        <f>SUM(G5:G11)</f>
+        <v>1587740.7</v>
+      </c>
+      <c r="H12" s="189"/>
+      <c r="I12" s="189"/>
+      <c r="J12" s="190"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="191"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="192"/>
+      <c r="I13" s="192"/>
+      <c r="J13" s="193"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="194" t="str">
+        <f>RESUMEN!C5</f>
+        <v>PERÍODO: JULIO</v>
+      </c>
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="195" t="str">
+        <f>RESUMEN!A30</f>
+        <v>Sueldo encargada Miriam</v>
+      </c>
+      <c r="G16" s="195"/>
+      <c r="H16" s="195"/>
+      <c r="I16" s="195"/>
+      <c r="J16" s="196"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+      <c r="D17" s="189"/>
+      <c r="E17" s="189"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="189"/>
+      <c r="H17" s="189"/>
+      <c r="I17" s="189"/>
+      <c r="J17" s="190"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="1" t="str">
+        <f>RESUMEN!A30</f>
+        <v>Sueldo encargada Miriam</v>
+      </c>
+      <c r="D18" s="189"/>
+      <c r="E18" s="189"/>
+      <c r="F18" s="189"/>
+      <c r="G18" s="197"/>
+      <c r="H18" s="201" t="s">
+        <v>304</v>
+      </c>
+      <c r="I18" s="201"/>
+      <c r="J18" s="202"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="str">
+        <f>RESUMEN!A31</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="D19" s="189"/>
+      <c r="E19" s="189"/>
+      <c r="F19" s="189"/>
+      <c r="G19" s="197">
+        <f>RESUMEN!D31</f>
+        <v>240732</v>
+      </c>
+      <c r="H19" s="201" t="s">
+        <v>305</v>
+      </c>
+      <c r="I19" s="201"/>
+      <c r="J19" s="202"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="1" t="str">
+        <f>RESUMEN!A32</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="197">
+        <f>RESUMEN!D32</f>
+        <v>33606.9</v>
+      </c>
+      <c r="H20" s="201"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="202"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="str">
+        <f>RESUMEN!A33</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="D21" s="189"/>
+      <c r="E21" s="189"/>
+      <c r="F21" s="189"/>
+      <c r="G21" s="197">
+        <f>RESUMEN!D33</f>
+        <v>111256.4</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="190"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="1" t="str">
+        <f>RESUMEN!A34</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="D22" s="189"/>
+      <c r="E22" s="189"/>
+      <c r="F22" s="189"/>
+      <c r="G22" s="197">
+        <f>RESUMEN!D34</f>
+        <v>19877.400000000001</v>
+      </c>
+      <c r="H22" s="201" t="s">
+        <v>306</v>
+      </c>
+      <c r="I22" s="201"/>
+      <c r="J22" s="202"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="1" t="str">
+        <f>RESUMEN!A35</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="D23" s="189"/>
+      <c r="E23" s="189"/>
+      <c r="F23" s="189"/>
+      <c r="G23" s="197">
+        <f>RESUMEN!D35</f>
+        <v>50000</v>
+      </c>
+      <c r="H23" s="201" t="s">
+        <v>305</v>
+      </c>
+      <c r="I23" s="201"/>
+      <c r="J23" s="202"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="1"/>
+      <c r="D24" s="189"/>
+      <c r="E24" s="189"/>
+      <c r="F24" s="189"/>
+      <c r="G24" s="189"/>
+      <c r="H24" s="201"/>
+      <c r="I24" s="201"/>
+      <c r="J24" s="202"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="198" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="199"/>
+      <c r="E25" s="199"/>
+      <c r="F25" s="199"/>
+      <c r="G25" s="200">
+        <f>SUM(G18:G24)</f>
+        <v>455472.70000000007</v>
+      </c>
+      <c r="H25" s="189"/>
+      <c r="I25" s="189"/>
+      <c r="J25" s="190"/>
+    </row>
+    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="191"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="192"/>
+      <c r="F26" s="192"/>
+      <c r="G26" s="192"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="192"/>
+      <c r="J26" s="193"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="H23:J24"/>
+    <mergeCell ref="H10:J11"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J20"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J7"/>
+    <mergeCell ref="H9:J9"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>